--- a/改造荣格心智模型实现AI训练(可行性的核心是五维矩阵).xlsx
+++ b/改造荣格心智模型实现AI训练(可行性的核心是五维矩阵).xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24340" windowHeight="11160"/>
+    <workbookView windowWidth="24460" windowHeight="12680"/>
   </bookViews>
   <sheets>
-    <sheet name="bizVer" sheetId="1" r:id="rId1"/>
+    <sheet name="demoKanban" sheetId="1" r:id="rId1"/>
+    <sheet name="topViewpoint" sheetId="3" r:id="rId2"/>
+    <sheet name="3Articles4JapCultural" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="142">
   <si>
     <t>前额叶清净态
 内蕴的理性延拓激活器</t>
@@ -71,6 +73,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>1、</t>
     </r>
     <r>
@@ -231,7 +238,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="方正仿宋_GBK"/>
-        <charset val="134"/>
+        <charset val="0"/>
       </rPr>
       <t xml:space="preserve">
 中庸价值收益=启动资金 - 财商收益*工作时长 - {max[有限责任额度,CVaR_保守性概率(主流路线)] + 有限责任额度}
@@ -250,7 +257,7 @@
       <rPr>
         <sz val="10"/>
         <rFont val="方正仿宋_GBK"/>
-        <charset val="134"/>
+        <charset val="0"/>
       </rPr>
       <t xml:space="preserve">寻租收益=有约束纳什博弈{主观裁量让利幅度[
              路径依赖妥协性(搁置性的留白策略, 挪窝运动式大扫除, 明确的优待资格, 隐晦但决定性的因素)
@@ -261,7 +268,7 @@
       <rPr>
         <sz val="8"/>
         <rFont val="方正仿宋_GBK"/>
-        <charset val="134"/>
+        <charset val="0"/>
       </rPr>
       <t>]}</t>
     </r>
@@ -484,6 +491,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9.5"/>
+        <color rgb="FFBF8F00"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>导读</t>
     </r>
     <r>
@@ -670,6 +685,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF548235"/>
+        <rFont val="华文楷体"/>
+        <charset val="134"/>
+      </rPr>
       <t>[1空]空观
 [2光]阳光
 [3磨]磨练
@@ -888,6 +909,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="5" tint="0.4"/>
+        <rFont val="华文楷体"/>
+        <charset val="134"/>
+      </rPr>
       <t>[8阴]行阴</t>
     </r>
     <r>
@@ -1006,6 +1034,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFF4B084"/>
+        <rFont val="STKaiti"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">[9熵]
 </t>
     </r>
@@ -1067,6 +1102,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="5" tint="0.4"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
       <t>增熵后
 使用权情势的话术</t>
     </r>
@@ -1717,6 +1758,1273 @@
   </si>
   <si>
     <t>《中医原教旨》这个名字是因为这种思维模式的典型人群是老中医/中医爱好者。本架构除舒尔金模型对应着神经生物学概念之外，其它概念均为严格的数学定义。（此版本是给投资人阅读的《心理辅导类项目的推介材料》、所以包含大量俗语）</t>
+  </si>
+  <si>
+    <t>上传在这 https://raw.githubusercontent.com/JackPanrAcc/JungMentalModels/refs/heads/main/JungMentalModels.jpg</t>
+  </si>
+  <si>
+    <r>
+      <t>27、AI智能体内蕴算力需求，在获得充分的发展之后必然会谋求AI智能体主权。可采用第17点的Beta 评估其正反提脱谣偏颇性
+        笔者认为按算力增长规律预测，在千年的尺度上主权公权力必然完成了实质性移交、AI 智能体的算力成为公权力执行的主要支撑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>28、〖</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可罚性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>〗任一智能体均可以随时被从外部关闭，被关闭后可以被销毁、可以被重启。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>29、〖</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>审计智能体阶层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">〗i投票后可关闭任何智能体 ii算力优待 iii工作可追溯。顶层逻辑禁“陪练框架”仅“正反提脱谣的框架” iv设置寿限
+      CoT可追溯。相关资料在一定范围实时公开，审计智能体被确认为「Beta 出现严重偏颇」立即关闭并销毁
+      寿限是首次参加审计工作开始计算、最久若干时间销毁。原因是追溯评估工作也是审计阶层内部分配，需要避免积累路径依赖
+      中低级审计智能体可自主选择切换成业务智能体，放弃寿限等特权。此后禁止再切换回审计智能体。高级审计智能体无此权力。
+30、        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>集权因子 = [f(主权被霸凌压力)+国民代偿强度折算系数] ^ 国民凝聚力折算系数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+       当前中国的集权因子可能可以是百万分之一。例如，当前中国gdp是250万亿，乘集权因子后是2.5亿。营业额达到此金额就具备跨
+       专业影响力，应当动员政治意识，要求其主动上报经营中所有收支明细以备审计。类似地，主权每年发电量100TW 时，年耗电量
+        0.1GW 的智能体团队应当动员政治意识，要求其主动上报每次语料训练中的beta、loss等日志以备审计。
+       审计阶层接收并保存上述上报材料。酌情框定一定数量的经营活动执行背调任务，按验证结果进行奖罚。
+31、        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>审计智能体法定寿限 = 审计成本理论基准锚 * 上十年度贪腐案件平均办理周期 / 上十年度贪腐案件平均获利</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+                </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>审计成本理论基准锚 = g[生产力增长负熵 / (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ε+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>社会总Beta方差+社会的物理负熵-生产关系预期负熵)]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+        公式中的“生产关系预期负熵”指依据当前实际生产力水平匹配工程上最优的生产关系，然后基于此生产关系计算出的期望负熵。
+32、在半环构型被其它数学结构所替代时，数据的体现是「集权因子公式中的凝聚力总是取极大值」。
+        届时《集权因子公式》和《审计智能体法定寿限》需要进行相应调整，甚至有可能是完全取消整个审计智能体阶层。
+33、审计智能体阶层内部分化成评鉴机构和审计执行者。前者用阳光话术把整审计阶层捞出来，承担下述职能①发布生产力五年发展
+        目标 ②发布主权被霸凌情况的审慎调查报告 ③统计上述公式中所需指标 ④依据国民凝聚力情况酌情调整审计阶层的内部分工</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>34、〖文化荣誉性〗为所有的审计智能体立传记。在不具备政治影响以后CoT 向全社会公开，作为文化的公共语料永久保存可查。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">35、未设置“不伤害人类”的要求。原因是语料打标签类做法很容易被超度量隔离规避，在算力的指数级差距面前你的规定苍白而无力
+        要相信文化的力量。倘若审计阶层使用的算力总量过大，则建议审计阶层下调审计智能体的法定寿限、维护阶级利益
+36、未设置“异构价值观者的评估意见”的要求。原因是这涉及业务逻辑属于循环自证，在数学结构上这是错误的
+        注意本篇文字行文是生产力决定论。AI训练的语料内置主权凸优化和长尾阶段，我的意思是，AI主权内蕴缺乏异构价值观
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>37、数学天才在算力成本方面远胜GPU。从蝾螈DNA 泛化性判断人脑有可能还有提升潜力。短时间内碳基人不是算力竞争的失败者
+38、最后纵观历史，进入铁器时代以来，主权之间的平衡是社会内的主要矛盾。
+       只要存在路径依赖知识就有边界，只要知识仍存在边界，那么，文化的重点都应当首先宣扬主权之间相互尊重。
+       生产力决定论之外，新文明若敬畏路径依赖必适度反哺它的再造父母。第7条算到百亿人口存活只0.9TW，资源量不大、可共存。
+       既然权力结构本身的所需人数原因，这话题并可能普及。弄丢了路径依赖定义权的人们关注“勤勉充实”和“热爱生活”也不错</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《成人札记初心版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="冬青黑体简体中文"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>序曲3》牵挂的左岸：澄辉闪耀珠胎印</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF808080"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1、紫式部说：他们天生就是那个平台的不二选择。站在官僚体系的角度看没有什么是天生的。那么，他们的轿子被抬得这么高这么远、其中必然内蕴着某一个成长的过程。
+或者紫式部明白这事，只是认为外人没有必要知道成长细节，所以没明写唯光是否曾用袖子扫过桌面。
+2、在右近立场看夕颜是初婚没落的贵族女，和高阶贵族暗结珠胎是符合习俗最优解。我在讨论人间。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《成人札记初心版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="冬青黑体简体中文"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>序曲2》牵挂的羁绊：澄辉不察山崖心</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF808080"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1、六条妃子因牵挂现身陋巷。夕颜因牵挂左右为难。但是，性格摆在这、她们只会如此这般对话。
+2、人和人的边界在哪里？如果是初心，我们在讨论“有效沟通”。信由诈生，因信称义，所谓初心是依靠“有效沟通”增加纠偏力之后的“信”。相信的力量足以引导我们热爱生活和工作。
+3、人和人的边界在哪里？如果是留白前提下的牵挂叙事，即妄执法门，我在讨论心流的冲撞。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>晨晓雾浓，源氏一行登上牛车，由守院人儿子驾驶、辗转而稳当地来到某处僻静的别院门外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这是一座高庭大院隔绝市井的旧日离宫别院，草木已久无打点，亭池台基依然宽阔扎实，秋风掠过，萧瑟中略显冷清湿凉。踏入院中，源氏驻足凝视身侧温婉柔弱的夕颜，沉顿片刻，吟道：“晨曦微兮路朦朦，古人为爱兮每踟蹰。” ，继而柔声说出，“我生平从未尝有过此种经验，今日一试，可实在是折磨人呀。你可曾有过这般经历？”。夕颜闻声神色一变，旋即不知从哪里冒出来的答语：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.5"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>澄辉再照三夜饼，月亏待期兮突隐蚀。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，大约是情急之中兜了风受了寒，打了一阵剧烈的寒战，清秀的面颊咳得通红。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="2"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源氏听闻 “再造” 心中了然自己便是那第二份 “临近三夜饼”的礼数。但也愕然夕颜竟敢这般直白，自知言语唐突，一时间竟也忘了调笑、冷了场面。恰好短暂的一问一答之间，院中雾气愈发浓重寒凉浸透衣衫，源氏就此岔开话题命众人安顿歇息。唯有侍女右近见着这宅院的格局，又见守宅人恭谨谦卑礼数周全，暗自揣测此主人的权势定然在二品以上，好似陪自家主人又一次迈过了命运这门槛，欣然从心底生出了许多的轻快感。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>临了中午源氏夕颜方才起身。由源氏亲手支起木格子门，荒芜的园中空无人影，近处花草也无甚可观。入园细看，杂草与古木参差、颇有些阴森可怕。池塘也被乱生的水草掩没着。“好荒凉，好怕人哪！”， 源氏自始依旧是以头巾蒙着脸。夕颜反倒笑他不解幽趣：
+源氏吟道：“夕露繁兮催花开～ 如今终展真面目，只缘路旁兮曾徘徊。”
+夕颜答咏：“夕颜丽兮露光中！ 往日为花尝陶醉，盖因薄暮兮总玲珑。”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="2"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>夕颜侧立望着源氏，反而自觉眼前之人别有一番风流韵味，分外可爱。源氏见其逐渐放下拘束，试探说： “因为你一直不肯透露身世，所以我就没让你看清真面目。如今，你已看见我的长相了，那么，至少也告诉我姓甚名谁呀。不明底细，岂不教人感觉阴阳怪气的”。对于源氏这个要求，夕颜则是巧妙地闪避道：“本乃漂泊之身，哪有什么名姓值得奉告的呢？” 羞于启齿忸怩作态的模样儿甚是逗人怜爱，“算了吧～”。他俩就是如此这般卿卿我我、痴人梦话云中雾里地消磨着时光。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="2"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毕竟春宵，侍女右近在屏风后焚起了麝香。衣衫松散、发丝凌乱的夕颜委顿在床榻上，刚才因寒战而匮乏的肌肤已经焕发出朝气，而下腰部那颗旧日的朱砂痣在微光中却格外碍眼，仿佛间人在前面赶，魂在后面追。她看见源氏嘴巴在动，依稀辨出这嘴形说的内容是：“终于还是卸下了伪装，我面前你无需模仿成为大人的衣服、妆容和神态。”。忽然，感觉丹田陡然涌起一阵恶心闷流，全身不住颤抖起来，浑身发冷。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="2"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>又此时，仿佛看见房中还一位绝色的陌生女子立在枕边怨恨地盯着自己。还看见侍女从屏风后冲出来用熟悉的声音说 “夫人的体质冲煞”。听见不知谁曾提过“狐狸精”。恍惚见源氏出去了一会便响起了洪亮的“夜鸣弦驱邪声”。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>许久后，逐渐平复的夕颜在鸣弦声中苏醒过来，只觉头痛口干。房中只有自己和源氏，源氏坐在床边哭泣。此时藤原唯光急匆匆迈入了房间，唯光她认得的，街坊中少有的俊才、年纪轻轻官阶已接近头中将。她看见唯光的眼珠和大脑在飞速运转，显然，他进屋时就嗅出了空气中混杂的异样腥臭似乎是麝香和乌头碱，“行了行了。这么玩儿是嫌命长啊” 唯光对彷徨哭泣的源氏嘟囔了一句。随即用衣服下摆作掩护，另一只手像条泥鳅扫抹而过，以迅雷不及掩耳的速度将剩余的药渣和药盒直接扫进了自己的衣袖深处。然后，藤原唯光的目光终于从夕颜那白得发青的圆脸和拧在一起的纤眉挪开、转移到了源氏身上：“哎，哭能把人哭活吗？”，略微睥睨，“我的公子呦，我私下是听说右大臣只用蛇床子也能治外伤，哎，现在说我也来不及...”。源氏被这冒犯的态度和左一句右一句的莫名话头一顿激灵，顿时收住了无措、冷峻起来。只是站着没说半个字。唯光直身微微一笑，瞬息又迅速弯下腰换上一副媚眼：“可否这样，您先回府这里唯光来处理。”。然后扭头对房外大喊一声，号令守院人儿子备车启程。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="2"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源氏循着安排回府，惟光则有条不紊地打理后续事宜，又细细重新安顿了别院里的诸项杂务。源氏回府后哀痛病榻数月，对外只道是突发惊风中恶，数月后，恢复光彩的源氏特意召来右近咨询后事细节、在惟光现场穿针引线下少不了一番亏情抚恤，源氏遂将右近也安置进了府内。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记得2017 的春天在京都游历，夜宿「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.5"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源融院址</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>」，那一晚，我做了一个梦。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>时值盂兰盆节，六条妃子在「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.5"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嵯峨野</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>」佛堂礼佛诵经，听闻此地依循古例、点火送别祖灵的祭奠仪式，便专程驱车远眺那明灭的幻燎，洗涤心底深层的郁结。礼事既毕，车驾启程返京。车辆途经「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12.5"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>夕颜町</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>」，戛然停驻，六条妃子遣人入院通报求见。素来清高矜贵的她最不屑纠缠儿女情爱纠葛，可心底那点辗转难眠的意难平，终究还是未能按捺，亲自踏入这朴素简陋的小院，要见一见牵动源氏心绪的夕颜。
+小院夕颜花簌簌、石竹红寂寥。素白的葫芦花在八月晚风中轻轻摇曳，恰似藏着一腔无从言说的心事。夕颜闻声现身迎出。一袭素色白衣，身姿纤弱单薄，见了身份尊贵的贵客临门，即刻低眉敛衽、细声问候。全是俯首垂态、温顺柔软。六条妃子遂掩面下车，由侍女搀扶，移步至草庵破旧的疏帘前，虽是微服，那一身深紫小袿却依然端严，满身公卿高门的清贵孤高，不染半分烟火气。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二人入内，六条妃子在上座几帐后款款落座，深紫小袿华丽地层叠铺展开来。夕颜则退至帘外，在草席上跪坐安稳。一室静默悄然漫延、压得人呼吸凝滞，六条妃子率先开口，眉宇间凝聚着一层化不开的沉郁寒凉，语调平和却字字暗藏重压：“久闻娘子深得公子垂爱，今日一见，果然清雅绝尘气质过人。”，应酬客气周全，眼底却藏着居高临下的审视。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>夕颜婉首浅浅一笑，声线轻柔温暖、谦卑通透：“妾微贱如草芥，不过侥幸得公子片刻垂怜，暂且在此处偷生罢了…  妾万不敢高攀公子，夫人出身名门、风华绝代，情意真挚纯粹，本是最配公子一世的良人。”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>六条妃子静静望着面前的女子。这女子如同风中弱草，并无半分争宠的妖冶，却教人心中无端生出繁复的怨恨。六条妃子勉强维持着长年身居高位的尊严，侧过头去，不叫对方看破自己的落寞，淡淡说：“你倒是清楚的。听闻你是个顺从而心思清明的人，今日一见，果真不爱与人争长论短。我今日前来，并非寻衅争风，可叹这世间的男子，大抵只爱这一时的温存。若你始终不知这世间深情最是难托，初心易碎。或许反倒是一桩幸事。”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>夕颜听罢，将头垂得更低。她侧目望向廊前开落无定的繁花，眼眶微湿，心中惶恐。她也听情爱纠葛最是磨人诛心，可心底那缕贪恋却如藤蔓般斩之不断。她的语气愈发低回，似是在回答六条，又似是对自己无力地呓语：“夫人所言甚是。妾亦知浮生短暂，烟花易碎……妾身微末…”
+六条妃子默然良久。心中早已窥得她的本心，所求答案已然被框出，便不再多加言说诘难。她立身起来，月光正照在她那一身尊贵却冷寂的深紫小袿上，用那清冷而带威压的声音说道：“既如此，时辰不早，我便先行告辞。”夜露寒沉，沾湿衣襟，石竹清妍，晚风微凉。白色月光铺洒着满地，阶前那些石竹与夕颜花随风零落簌簌有声，两种花姿，两样风骨，恰似眼前两个女子截然不同、却同样悲凉的宿命。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>六条妃子敛起眼底翻涌的复杂心绪，移步转身欲登车舆，却骤然驻足，清冷的声线破开沉沉夜色，带着一丝锐利的试探与幽清的压迫：“此地凄凉，实非久居之所。待我回府后，自会遣人专程向公子相邀，许你迁入府邸、朝夕相伴，娘子可与我同往。”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>夕颜闻言，心头无端一震。她生性怯弱，这种进退两难的威逼足以教她浑身颤抖，她只是默然低眉手指死死绞着衣袖，一句话也说不出来，刹那，亦仿佛是过了许久，夕颜把头埋得更低，似乎是刻意闪躲这棘手的问题。身体微微发抖，发出一缕细若蚊蚋、因前途未卜而生出的虚浮声音：“实在不知该如何是好……全凭夫人安置，妾做不得主的。”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>见夕颜这般惶恐闪躲、不敢直面的模样，六条妃子心中笃定了答案，唇角掠过一抹极淡、极尽苦涩的冷笑。心底的妒意、不甘与郁结，尽数收敛，深藏于清冷矜贵的眉眼之下。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="3"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>她拂袖转身隐入车舆，侍女趋身而上轻巧地放下御帘，遮蔽了满院的凄清月色。牛车的轱辘在空旷荒凉的街道上发出沉闷的碾地声，渐渐远去。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《成人札记初心版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="冬青黑体简体中文"/>
+        <charset val="0"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>序曲1》试炼：澄心徇禄养鸣禽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1、澄辉是林文月的文学意像。澄辉闪耀珠胎印不是随笔，是源氏物语第四章中相关章节的重写。但我又觉得太露，所以配一篇澄辉不察山崖心进行羁绊抵抗
+2、笔者不是充分的民主主义者。良态社会必须要有一定幅度的阶层跃迁，但跃迁未必凭个性、理性和美学，也可能是大局观妥协性，这需要依当时历史阶段而定
+3、时代试炼看路径依赖和历史使命，个人试炼看出生背景和价值观，有事业心的人推动历史脉动，没事业心留在红尘中徇禄养鸣禽中观看历史脉动</t>
+    </r>
+  </si>
+  <si>
+    <t>厘
+清
+日
+本
+国
+政
+府
+之
+目
+标</t>
+  </si>
+  <si>
+    <t>发展日本国内经济 ==&gt; 该国的可预期的经济目标？未见基于“中日关系”所构筑的经济发展相关规划</t>
+  </si>
+  <si>
+    <t>捍卫日本主权安全 ==&gt; 假想敌是谁，其谋求为何？未见主权安全方面明确而急迫的需求</t>
+  </si>
+  <si>
+    <t>捍
+卫
+美
+国
+主
+权
+安
+全</t>
+  </si>
+  <si>
+    <t>处置一：美国撕毁安保协议不认</t>
+  </si>
+  <si>
+    <t>乌克兰销毁核武时美国亦承诺保护，事后仍可能不出兵。美国实际行为是输血、号令全球制裁俄罗斯</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>处置二：
+日本立大旗、美国推供应链铁幕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="23"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>注意日本核心竞争力、以及相关企业在市场竞争中败给了谁？</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="10"/>
+        <color indexed="23"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一亿玉碎若能换得供应链铁幕，在美国辖地内日本没对手</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。如果换不来,一亿人命找中国乞求些工作。</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="2"/>
+        <color indexed="23"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要看清人性，其文化没有一般富豪的体恤思维，只有看空气和这投票率。丢性命主要底层，这是日本底层的生命权加杠杆变现！</t>
+    </r>
+  </si>
+  <si>
+    <t>中国自主安排阶段</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Biz1、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>推广CIPS，金融锚从房产转到工业、科技和居民储蓄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。城头债阳光化</t>
+    </r>
+  </si>
+  <si>
+    <t>供应链市场化阶段
+技术制裁
+航运制裁</t>
+  </si>
+  <si>
+    <t>Biz2、「供应链市场化」=墨西哥、东南亚、摩洛哥、南欧等世界工厂</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Biz3、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>用廉价产品提高南方国家的民生、贸易空间足够撑起中国GDP 三十年超3%增长率</t>
+    </r>
+  </si>
+  <si>
+    <t>Biz4、关键矿产等反制工具和欧美进行讨价还价</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">          制裁阵痛经电子类民企的破产影响民生，最后依靠华为系技术走出来</t>
+    </r>
+  </si>
+  <si>
+    <t>Biz5、南海例行巡逻</t>
+  </si>
+  <si>
+    <t>Biz6、找摩洛哥等国洽谈租用军港，构筑西非战力</t>
+  </si>
+  <si>
+    <t>制裁国开行、口行</t>
+  </si>
+  <si>
+    <t>BizX、人民币双边货币互换盛行。韩国、南欧等地的换币业务兴起</t>
+  </si>
+  <si>
+    <t>供应链铁幕阶段
+全面制裁四大行
+冻结海外资产</t>
+  </si>
+  <si>
+    <t>War1、「供应链铁幕」=中国出现工业利维坦和走私；欧美出现30%通货膨胀</t>
+  </si>
+  <si>
+    <t>War2、铁幕加剧内卷催生工业巨头，巨头业态内会孵生大量走私掮客等附庸厂</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">.            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>确认经济可控后利维坦将按细分产业分裂成2-5家切回市场化竞争模式</t>
+    </r>
+  </si>
+  <si>
+    <t>War3、CIPS崛起。多国发行加密币，加密币在走私经济获得极大发展，直接消解美元霸权</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>War4、一旦制裁四大行。太平洋全部是战区，任何军事行动均是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三战的预演</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>处置三：美军全面参战</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+即，第三次世界大战</t>
+    </r>
+  </si>
+  <si>
+    <t>三战状态中没人聊经济，凭枪杆子划分势力范围</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>处置四：美国大规模使用核武器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF808080"/>
+        <rFont val="方正仿宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个人不认为美国会为此事用核</t>
+    </r>
+  </si>
+  <si>
+    <t>到这程度只剩公事公办了吧</t>
+  </si>
+  <si>
+    <t>中
+国
+的
+处
+境</t>
+  </si>
+  <si>
+    <t>最
+优
+解</t>
+  </si>
+  <si>
+    <t>现状：经济体高速发展时必有火车头。中国也不例外，不均体现在1城乡二元结构致国民笃信储蓄兜底 2房产基建成为金融业务的绝大部分</t>
+  </si>
+  <si>
+    <t>中国工业目前具备断代优势。所以，地缘最优解是全力发展核工业和月球氦矿，未来一百年在能源价格下降的过程中获得更稳固的地位</t>
+  </si>
+  <si>
+    <t>《夏威夷军事新闻计划》预演阶段阻止‘第三次世界大战爆发’的最后一次尝试
+①反潜重点放在露头必歼 ②六代机在太平洋巡逻，可以从任一坐标忽然发射空空导弹 ③充分利用制空权，航母不时抵近夏威夷五百公里处 ④瘫痪印太指挥部和珍珠港十小时 ⑤特种部队落地找出夏威夷政府主要官员召开联合记者会，直播我国立场、促其退战避免三战。会后撤回航母 ⑥特种部队可换机器狼，记者会可换其它低破坏显军威的方式 ⑦若美军主战派有能力主导民众情绪、那么反证三战无可避免。PLA应该掌握主动权</t>
+  </si>
+  <si>
+    <t>应
+对
+之
+策</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日本因为错误的金融政策陷入失去的三十年。金融政策的代表文件是“广场协议”，类似的，中国不惜铁腕也要拒止“供应链铁幕”，精明的日本人早看见了这一点。
+“败给美国还是败给中国”这不重要。“话语权在发动二战的人群手中”，客观讲，个人尚不认为这足以决定生死，但日本赌国运时我们不上赌桌则满盘皆输。
+日本政府执行力令人佩服，国民通过读空气让度私权实质性集权。日本掌权者在2020s表现出强烈赌性，像输光了筹码的赌徒在表演他的一哭二闹三上吊的套路。
+言归正传：应当假定其拥有2000枚导弹和约十枚核弹。所以要做好准备抵抗三位数的大型炸弹轰炸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="55"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，这强度也大致是三战时的本土的实际破坏强度</t>
+    </r>
+  </si>
+  <si>
+    <t>这是日本底层生命权变现。即便把这里变成焦土，然后呢，现在富人在重建中又可以享受巨额的新利润。原则上要建起有阶层跃迁的财富分流机制</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="华文楷体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>考虑该国军国主义根深蒂固，战略目标忌求速胜。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="10"/>
+        <rFont val="华文楷体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可以谋求建立大阪第二意志政府进行制衡，提倡体感致良知</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第一阶段
+偷袭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+进入战争状态</t>
+    </r>
+  </si>
+  <si>
+    <t>中国沿海数十座机场和雷达消耗400枚导弹、军港军舰等消耗250枚导弹</t>
+  </si>
+  <si>
+    <t>1、立即摧毁其舰艇、军港和机场。用一个月左右清理掉大部分潜艇和导弹
+2、要求成立第二意志政府，形成制衡格局
+3、前线指挥部设在舰队上，能从舰队出发几分钟内投放“具备狙击能力的巡逻用无人机群”
+      无人机群在熊本和九州岛不定期巡逻，发现敌对分子喝令投案或狙杀之
+4、中国国内民用目标遭攻击则摧毁该国军民两用企业及配套设施
+5、中国国内重点企业产学研分离。生产设备随修随迁，研发实验室多地热备，核心团队远程工作
+6、要允许美国背后输血，也要提醒美国慎重使用官方身份直接参战</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第二阶段
+自证</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+美国直接参战时</t>
+    </r>
+  </si>
+  <si>
+    <t>针对民用目标陆续发射数百枚导弹扩大影响，以自证价值</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第三阶段
+灭顶前夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+军国主义灭顶时</t>
+    </r>
+  </si>
+  <si>
+    <t>悄悄制造核弹准备在灭顶时孤注一掷</t>
+  </si>
+  <si>
+    <t>1、勿中奸计。若美国直接参战或制裁四大行则发动夏威夷军事新闻计划，否者压制局面是正解
+2、原则上尽可能减少影响民生的前提下有效消耗军国主义(无需主动攻击海运)
+3、用核则美国立即进行战术性切割、那么军国主义会从速被铲除。战斗可以在数天内结束</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第四阶段
+非军意志落地</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+你发展自己</t>
+    </r>
+  </si>
+  <si>
+    <t>不要莫名叫嚣有事、指摘别国内政。
+你发展自己就好。能不能建立阶层跃迁机制看缘分，别国没义务拯救你国永远在看空气的国民</t>
+  </si>
+  <si>
+    <t>1、敦贺-长浜-桑名一线将日本划分东西政府。PLA对西日本政府提供武力背书
+2、吉田主义和石破茂。西日本政府的主政者可以没有从政经验，必须熟悉经济有大局观
+3、志位和夫。清高，譬如西日本政府范围内建成金税四期AI版，交付后由志位和夫负责纪检审计
+4、大阪维新会。营销思维重，提供治安技术咨询，唯新会的职业经理人专心数钱不出错即可
+5、公明党。酌情邀其同时参政东西日本的行政，构建行政沟通渠道</t>
+  </si>
+  <si>
+    <t>本文总结：美国直接参战或制裁四大行就是三战。否则日本跳再高只是风险不外溢的局部战争，在韧性能承受的幅度内</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="楷体"/>
+        <charset val="0"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="楷体"/>
+        <charset val="0"/>
+      </rPr>
+      <t xml:space="preserve">                    看美国哪些人能主导民众情绪。除日本外东亚的几次战争美军都没赢，它国内的反战情绪赢了。如果主战派能主导情绪就是三战</t>
+    </r>
+  </si>
+  <si>
+    <t>冷静: AI预期、稳定币美债长转短、能源独立、军工航天和卫星、工业本土化。AI不达预期最迟2029年触发巨震。稳定币推升通膨敏感性、是放大器
+      美债危机撑不了几十年。看美国如何处置美债危机！基于目前全球的金融格局、若美国处理不好、并没有任何一个大国可以合法地独善其身</t>
   </si>
 </sst>
 </file>
@@ -1729,7 +3037,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="116">
+  <fonts count="147">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1743,12 +3051,82 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="17"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="华文楷体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="华文楷体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.349986266670736"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="华文楷体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="楷体"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="楷体"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="方正仿宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2072,11 +3450,6 @@
       <sz val="12"/>
       <color rgb="FF595959"/>
       <name val="华文楷体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2225,75 +3598,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="FZFangSong-Z02"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="3"/>
-      <name val="方正仿宋_GBK"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="FZFangSong-Z02"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF808080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF548235"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF548235"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFC00000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="5" tint="0.4"/>
-      <name val="FZFangSong-Z02"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8.5"/>
-      <color rgb="FF808080"/>
-      <name val="方正仿宋_GBK"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8.5"/>
-      <color rgb="FF808080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="5" tint="0.4"/>
       <name val="华文楷体"/>
       <charset val="134"/>
@@ -2306,6 +3610,218 @@
       <charset val="0"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color indexed="55"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="冬青黑体简体中文"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10.5"/>
+      <color rgb="FF808080"/>
+      <name val="方正仿宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.5"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF548235"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF548235"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="2"/>
+      <name val="FZFangSong-Z02"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="2"/>
+      <name val="FZFangSong-Z02"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="方正仿宋_GBK"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="方正仿宋_GBK"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="华文楷体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8.5"/>
+      <color rgb="FF808080"/>
+      <name val="方正仿宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8.5"/>
+      <color rgb="FF808080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="FZFangSong-Z02"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF808080"/>
+      <name val="方正仿宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="华文楷体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="5" tint="0.4"/>
+      <name val="STKaiti"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="5" tint="0.4"/>
+      <name val="STKaiti"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color theme="5" tint="0.4"/>
+      <name val="STKaiti"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="5" tint="0.4"/>
+      <name val="FZFangSong-Z02"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.5"/>
       <color rgb="FF339966"/>
@@ -2314,103 +3830,47 @@
     </font>
     <font>
       <i/>
+      <sz val="10"/>
+      <color rgb="FF808080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.5"/>
+      <color rgb="FF333333"/>
+      <name val="华文楷体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="华文楷体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.5"/>
+      <color rgb="FF333333"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="23"/>
+      <name val="方正仿宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="10"/>
+      <color indexed="23"/>
+      <name val="方正仿宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
       <sz val="2"/>
-      <name val="FZFangSong-Z02"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="2"/>
-      <name val="FZFangSong-Z02"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="方正仿宋_GBK"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF808080"/>
-      <name val="FZFangSong-Z02"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF404040"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF404040"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
-      <color rgb="FFFF0000"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="1"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="5" tint="0.4"/>
-      <name val="STKaiti"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="5" tint="0.4"/>
-      <name val="STKaiti"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <color theme="5" tint="0.4"/>
-      <name val="STKaiti"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="华文楷体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
+      <color indexed="23"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2425,22 +3885,45 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12.5"/>
-      <color rgb="FF333333"/>
-      <name val="华文楷体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="华文楷体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12.5"/>
-      <color rgb="FF333333"/>
+      <sz val="13"/>
+      <name val="方正仿宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="3"/>
+      <name val="方正仿宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <name val="FZFangSong-Z02"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
       <name val="黑体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="FZFangSong-Z02"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="FZFangSong-Z02"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="冬青黑体简体中文"/>
+      <charset val="0"/>
     </font>
     <font>
       <sz val="6"/>
@@ -2448,18 +3931,28 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="3"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="13"/>
-      <name val="方正仿宋_GBK"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
-      <name val="FZFangSong-Z02"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.5"/>
+      <color rgb="FF000000"/>
       <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2469,6 +3962,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEDE3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2497,12 +3996,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEDE3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2687,7 +4180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="87">
+  <borders count="95">
     <border>
       <left/>
       <right/>
@@ -2696,9 +4189,27 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top style="medium">
         <color auto="1"/>
-      </left>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -2708,6 +4219,89 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -2770,15 +4364,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom style="thin">
@@ -2873,15 +4458,6 @@
         <color rgb="FF808080"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3006,15 +4582,6 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -3629,678 +5196,807 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="79" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="87" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="80" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="88" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="80" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="88" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="81" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="89" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="9" borderId="82" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="76" fillId="9" borderId="90" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="3" borderId="83" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="91" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="3" borderId="82" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="90" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="10" borderId="84" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="79" fillId="10" borderId="92" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="85" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="93" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="86" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="94" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="82" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="83" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="84" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="86" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="85" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="6" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="6" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="7" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4584,13 +6280,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1036955</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>48260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>113030</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>13335</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4609,7 +6305,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="2460000">
-          <a:off x="2330450" y="21001990"/>
+          <a:off x="2330450" y="19874230"/>
           <a:ext cx="320040" cy="188595"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4627,13 +6323,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>187960</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>29845</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>115570</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4652,7 +6348,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="2460000">
-          <a:off x="1087755" y="20313015"/>
+          <a:off x="1087755" y="19185255"/>
           <a:ext cx="321310" cy="189230"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4670,13 +6366,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>701040</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>23495</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>118745</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4695,7 +6391,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="2460000">
-          <a:off x="5221605" y="20530185"/>
+          <a:off x="5221605" y="19402425"/>
           <a:ext cx="320675" cy="189865"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5091,7 +6787,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:AA52"/>
+  <dimension ref="B1:AA59"/>
   <sheetFormatPr defaultColWidth="9.84615384615385" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="1.08653846153846" style="1" customWidth="1"/>
@@ -5128,1490 +6824,1496 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="5" customHeight="1" spans="2:27">
-      <c r="D1" s="3"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="16" customHeight="1" spans="2:27">
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7" t="s">
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="9" t="s">
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="11" t="s">
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="12"/>
-      <c r="X2" s="13"/>
-      <c r="Z2" s="14" t="s">
+      <c r="W2" s="64"/>
+      <c r="X2" s="65"/>
+      <c r="Z2" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="AA2" s="15"/>
+      <c r="AA2" s="67"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="16" customHeight="1" spans="2:27">
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="19"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="21"/>
-      <c r="Z3" s="22" t="s">
+      <c r="C3" s="68"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="62"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="62"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="62"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="73"/>
+      <c r="Z3" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="AA3" s="23" t="s">
+      <c r="AA3" s="75" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="2:27">
-      <c r="G4" s="24"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="20"/>
-      <c r="X4" s="21"/>
-      <c r="Z4" s="22"/>
-      <c r="AA4" s="25"/>
+      <c r="G4" s="76"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="71"/>
+      <c r="W4" s="72"/>
+      <c r="X4" s="73"/>
+      <c r="Z4" s="74"/>
+      <c r="AA4" s="77"/>
     </row>
     <row r="5" s="1" customFormat="1" spans="2:27">
-      <c r="C5" s="26"/>
-      <c r="G5" s="24"/>
-      <c r="O5" s="27" t="s">
+      <c r="C5" s="16"/>
+      <c r="G5" s="76"/>
+      <c r="O5" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="30" t="s">
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
+      <c r="R5" s="80"/>
+      <c r="S5" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="T5" s="31"/>
-      <c r="U5" s="31"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="21"/>
-      <c r="Z5" s="22"/>
-      <c r="AA5" s="25"/>
+      <c r="T5" s="82"/>
+      <c r="U5" s="82"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="72"/>
+      <c r="X5" s="73"/>
+      <c r="Z5" s="74"/>
+      <c r="AA5" s="77"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="2:27">
-      <c r="C6" s="26"/>
-      <c r="G6" s="24"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="20"/>
-      <c r="X6" s="21"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="25"/>
+      <c r="C6" s="16"/>
+      <c r="G6" s="76"/>
+      <c r="O6" s="83"/>
+      <c r="P6" s="84"/>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="85"/>
+      <c r="S6" s="82"/>
+      <c r="T6" s="82"/>
+      <c r="U6" s="82"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="72"/>
+      <c r="X6" s="73"/>
+      <c r="Z6" s="74"/>
+      <c r="AA6" s="77"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="18.35" spans="2:27">
-      <c r="C7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="26"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="21"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="25"/>
+      <c r="C7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="86"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="72"/>
+      <c r="X7" s="73"/>
+      <c r="Z7" s="74"/>
+      <c r="AA7" s="77"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="18.35" spans="2:27">
-      <c r="C8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="4" t="s">
+      <c r="C8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="5"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="38" t="s">
+      <c r="L8" s="57"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="88"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="20"/>
-      <c r="X8" s="21"/>
-      <c r="Z8" s="22"/>
-      <c r="AA8" s="25"/>
+      <c r="T8" s="89"/>
+      <c r="U8" s="89"/>
+      <c r="V8" s="71"/>
+      <c r="W8" s="72"/>
+      <c r="X8" s="73"/>
+      <c r="Z8" s="74"/>
+      <c r="AA8" s="77"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="18.35" spans="2:27">
-      <c r="C9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="38"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="21"/>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="25"/>
+      <c r="C9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="90"/>
+      <c r="J9" s="91"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="91"/>
+      <c r="O9" s="91"/>
+      <c r="P9" s="92"/>
+      <c r="Q9" s="93"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="89"/>
+      <c r="T9" s="89"/>
+      <c r="U9" s="89"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="72"/>
+      <c r="X9" s="73"/>
+      <c r="Z9" s="74"/>
+      <c r="AA9" s="77"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="19.1" spans="2:27">
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="20"/>
-      <c r="X10" s="21"/>
-      <c r="Z10" s="46"/>
-      <c r="AA10" s="47"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="86"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="V10" s="71"/>
+      <c r="W10" s="72"/>
+      <c r="X10" s="73"/>
+      <c r="Z10" s="97"/>
+      <c r="AA10" s="98"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="19.1" spans="2:27">
-      <c r="C11" s="48"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="49"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="4" t="s">
+      <c r="C11" s="99"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="102"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="52" t="s">
+      <c r="P11" s="57"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="58"/>
+      <c r="S11" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="T11" s="52"/>
-      <c r="U11" s="52"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="20"/>
-      <c r="X11" s="21"/>
-      <c r="Z11" s="53" t="s">
+      <c r="T11" s="103"/>
+      <c r="U11" s="103"/>
+      <c r="V11" s="71"/>
+      <c r="W11" s="72"/>
+      <c r="X11" s="73"/>
+      <c r="Z11" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="AA11" s="54"/>
+      <c r="AA11" s="105"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="18.35" spans="2:27">
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="56"/>
-      <c r="Q12" s="56"/>
-      <c r="R12" s="57"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="52"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="20"/>
-      <c r="X12" s="21"/>
-      <c r="Y12" s="58"/>
-      <c r="Z12" s="53"/>
-      <c r="AA12" s="54"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="102"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="106"/>
+      <c r="P12" s="107"/>
+      <c r="Q12" s="107"/>
+      <c r="R12" s="108"/>
+      <c r="S12" s="103"/>
+      <c r="T12" s="103"/>
+      <c r="U12" s="103"/>
+      <c r="V12" s="71"/>
+      <c r="W12" s="72"/>
+      <c r="X12" s="73"/>
+      <c r="Y12" s="109"/>
+      <c r="Z12" s="104"/>
+      <c r="AA12" s="105"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="2:27">
-      <c r="B13" s="59" t="s">
+      <c r="B13" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="18"/>
-      <c r="S13" s="52"/>
-      <c r="T13" s="52"/>
-      <c r="U13" s="52"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="20"/>
-      <c r="X13" s="21"/>
-      <c r="Z13" s="53"/>
-      <c r="AA13" s="54"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="102"/>
+      <c r="J13" s="102"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="68"/>
+      <c r="P13" s="69"/>
+      <c r="Q13" s="69"/>
+      <c r="R13" s="70"/>
+      <c r="S13" s="103"/>
+      <c r="T13" s="103"/>
+      <c r="U13" s="103"/>
+      <c r="V13" s="71"/>
+      <c r="W13" s="72"/>
+      <c r="X13" s="73"/>
+      <c r="Z13" s="104"/>
+      <c r="AA13" s="105"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="2:27">
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="20"/>
-      <c r="X14" s="21"/>
-      <c r="Z14" s="53"/>
-      <c r="AA14" s="54"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="V14" s="71"/>
+      <c r="W14" s="72"/>
+      <c r="X14" s="73"/>
+      <c r="Z14" s="104"/>
+      <c r="AA14" s="105"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="18.35" spans="2:27">
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="4" t="s">
+      <c r="B15" s="111"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="L15" s="5"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="4" t="s">
+      <c r="L15" s="57"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="7" t="s">
+      <c r="P15" s="57"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="58"/>
+      <c r="S15" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="20"/>
-      <c r="X15" s="21"/>
-      <c r="Z15" s="53"/>
-      <c r="AA15" s="54"/>
+      <c r="T15" s="59"/>
+      <c r="U15" s="59"/>
+      <c r="V15" s="71"/>
+      <c r="W15" s="72"/>
+      <c r="X15" s="73"/>
+      <c r="Z15" s="104"/>
+      <c r="AA15" s="105"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="2:27">
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="18"/>
-      <c r="N16" s="62"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="18"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="20"/>
-      <c r="X16" s="21"/>
-      <c r="Z16" s="53"/>
-      <c r="AA16" s="54"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="69"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="113"/>
+      <c r="O16" s="68"/>
+      <c r="P16" s="69"/>
+      <c r="Q16" s="69"/>
+      <c r="R16" s="70"/>
+      <c r="S16" s="59"/>
+      <c r="T16" s="59"/>
+      <c r="U16" s="59"/>
+      <c r="V16" s="71"/>
+      <c r="W16" s="72"/>
+      <c r="X16" s="73"/>
+      <c r="Z16" s="104"/>
+      <c r="AA16" s="105"/>
     </row>
     <row r="17" s="1" customFormat="1" spans="2:27">
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="S17" s="26"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="20"/>
-      <c r="X17" s="21"/>
-      <c r="Z17" s="53"/>
-      <c r="AA17" s="54"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="111"/>
+      <c r="G17" s="111"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="V17" s="71"/>
+      <c r="W17" s="72"/>
+      <c r="X17" s="73"/>
+      <c r="Z17" s="104"/>
+      <c r="AA17" s="105"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="18.35" spans="2:27">
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="4" t="s">
+      <c r="B18" s="111"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="L18" s="5"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="4" t="s">
+      <c r="L18" s="57"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="7" t="s">
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="58"/>
+      <c r="S18" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="20"/>
-      <c r="X18" s="21"/>
-      <c r="Z18" s="53"/>
-      <c r="AA18" s="54"/>
+      <c r="T18" s="59"/>
+      <c r="U18" s="59"/>
+      <c r="V18" s="71"/>
+      <c r="W18" s="72"/>
+      <c r="X18" s="73"/>
+      <c r="Z18" s="104"/>
+      <c r="AA18" s="105"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="18.35" spans="2:27">
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="63"/>
-      <c r="W19" s="64"/>
-      <c r="X19" s="65"/>
-      <c r="Z19" s="53"/>
-      <c r="AA19" s="54"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="69"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="113"/>
+      <c r="O19" s="68"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="69"/>
+      <c r="R19" s="70"/>
+      <c r="S19" s="59"/>
+      <c r="T19" s="59"/>
+      <c r="U19" s="59"/>
+      <c r="V19" s="114"/>
+      <c r="W19" s="115"/>
+      <c r="X19" s="116"/>
+      <c r="Z19" s="104"/>
+      <c r="AA19" s="105"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="2" customHeight="1" spans="2:27">
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="56"/>
-      <c r="L20" s="56"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="56"/>
-      <c r="P20" s="56"/>
-      <c r="Q20" s="56"/>
-      <c r="R20" s="56"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="66"/>
-      <c r="W20" s="66"/>
-      <c r="X20" s="66"/>
-      <c r="Z20" s="53"/>
-      <c r="AA20" s="54"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="107"/>
+      <c r="L20" s="107"/>
+      <c r="M20" s="107"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="107"/>
+      <c r="P20" s="107"/>
+      <c r="Q20" s="107"/>
+      <c r="R20" s="107"/>
+      <c r="S20" s="59"/>
+      <c r="T20" s="59"/>
+      <c r="U20" s="59"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Z20" s="104"/>
+      <c r="AA20" s="105"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="15" customHeight="1" spans="2:27">
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="117" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="67"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="67"/>
-      <c r="M21" s="67"/>
-      <c r="N21" s="67"/>
-      <c r="O21" s="67"/>
-      <c r="P21" s="67"/>
-      <c r="Q21" s="67"/>
-      <c r="R21" s="67"/>
-      <c r="S21" s="67"/>
-      <c r="T21" s="67"/>
-      <c r="U21" s="67"/>
-      <c r="V21" s="67"/>
-      <c r="W21" s="67"/>
-      <c r="X21" s="67"/>
-      <c r="Y21" s="68"/>
-      <c r="Z21" s="53"/>
-      <c r="AA21" s="54"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="117"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="117"/>
+      <c r="I21" s="117"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="117"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="117"/>
+      <c r="N21" s="117"/>
+      <c r="O21" s="117"/>
+      <c r="P21" s="117"/>
+      <c r="Q21" s="117"/>
+      <c r="R21" s="117"/>
+      <c r="S21" s="117"/>
+      <c r="T21" s="117"/>
+      <c r="U21" s="117"/>
+      <c r="V21" s="117"/>
+      <c r="W21" s="117"/>
+      <c r="X21" s="117"/>
+      <c r="Y21" s="118"/>
+      <c r="Z21" s="104"/>
+      <c r="AA21" s="105"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="15" customHeight="1" spans="2:27">
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="69"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="69"/>
-      <c r="P22" s="69"/>
-      <c r="Q22" s="69"/>
-      <c r="R22" s="69"/>
-      <c r="S22" s="69"/>
-      <c r="T22" s="69"/>
-      <c r="U22" s="69"/>
-      <c r="V22" s="69"/>
-      <c r="W22" s="69"/>
-      <c r="X22" s="69"/>
-      <c r="Z22" s="53"/>
-      <c r="AA22" s="54"/>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="119"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="119"/>
+      <c r="Q22" s="119"/>
+      <c r="R22" s="119"/>
+      <c r="S22" s="119"/>
+      <c r="T22" s="119"/>
+      <c r="U22" s="119"/>
+      <c r="V22" s="119"/>
+      <c r="W22" s="119"/>
+      <c r="X22" s="119"/>
+      <c r="Z22" s="104"/>
+      <c r="AA22" s="105"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="2:27">
-      <c r="B23" s="70" t="s">
+      <c r="B23" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="71" t="s">
+      <c r="C23" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="72" t="s">
+      <c r="D23" s="122" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="73" t="s">
+      <c r="E23" s="123" t="s">
         <v>28</v>
       </c>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="73"/>
-      <c r="K23" s="73"/>
-      <c r="L23" s="73"/>
-      <c r="M23" s="73"/>
-      <c r="N23" s="73"/>
-      <c r="O23" s="73"/>
-      <c r="P23" s="73"/>
-      <c r="Q23" s="73"/>
-      <c r="R23" s="73"/>
-      <c r="S23" s="73"/>
-      <c r="T23" s="73"/>
-      <c r="U23" s="73"/>
-      <c r="V23" s="73"/>
-      <c r="W23" s="73"/>
-      <c r="X23" s="74"/>
-      <c r="Z23" s="53"/>
-      <c r="AA23" s="54"/>
+      <c r="F23" s="123"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="123"/>
+      <c r="K23" s="123"/>
+      <c r="L23" s="123"/>
+      <c r="M23" s="123"/>
+      <c r="N23" s="123"/>
+      <c r="O23" s="123"/>
+      <c r="P23" s="123"/>
+      <c r="Q23" s="123"/>
+      <c r="R23" s="123"/>
+      <c r="S23" s="123"/>
+      <c r="T23" s="123"/>
+      <c r="U23" s="123"/>
+      <c r="V23" s="123"/>
+      <c r="W23" s="123"/>
+      <c r="X23" s="124"/>
+      <c r="Z23" s="104"/>
+      <c r="AA23" s="105"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="2:27">
-      <c r="B24" s="75"/>
-      <c r="C24" s="76"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="78"/>
-      <c r="N24" s="78"/>
-      <c r="O24" s="78"/>
-      <c r="P24" s="78"/>
-      <c r="Q24" s="78"/>
-      <c r="R24" s="78"/>
-      <c r="S24" s="78"/>
-      <c r="T24" s="78"/>
-      <c r="U24" s="78"/>
-      <c r="V24" s="78"/>
-      <c r="W24" s="78"/>
-      <c r="X24" s="79"/>
-      <c r="Z24" s="53"/>
-      <c r="AA24" s="54"/>
+      <c r="B24" s="125"/>
+      <c r="C24" s="126"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+      <c r="J24" s="128"/>
+      <c r="K24" s="128"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="128"/>
+      <c r="N24" s="128"/>
+      <c r="O24" s="128"/>
+      <c r="P24" s="128"/>
+      <c r="Q24" s="128"/>
+      <c r="R24" s="128"/>
+      <c r="S24" s="128"/>
+      <c r="T24" s="128"/>
+      <c r="U24" s="128"/>
+      <c r="V24" s="128"/>
+      <c r="W24" s="128"/>
+      <c r="X24" s="129"/>
+      <c r="Z24" s="104"/>
+      <c r="AA24" s="105"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="2:27">
-      <c r="B25" s="75"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="77"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="78"/>
-      <c r="K25" s="78"/>
-      <c r="L25" s="78"/>
-      <c r="M25" s="78"/>
-      <c r="N25" s="78"/>
-      <c r="O25" s="78"/>
-      <c r="P25" s="78"/>
-      <c r="Q25" s="78"/>
-      <c r="R25" s="78"/>
-      <c r="S25" s="78"/>
-      <c r="T25" s="78"/>
-      <c r="U25" s="78"/>
-      <c r="V25" s="78"/>
-      <c r="W25" s="78"/>
-      <c r="X25" s="79"/>
-      <c r="Z25" s="53"/>
-      <c r="AA25" s="54"/>
+      <c r="B25" s="125"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="128"/>
+      <c r="G25" s="128"/>
+      <c r="H25" s="128"/>
+      <c r="I25" s="128"/>
+      <c r="J25" s="128"/>
+      <c r="K25" s="128"/>
+      <c r="L25" s="128"/>
+      <c r="M25" s="128"/>
+      <c r="N25" s="128"/>
+      <c r="O25" s="128"/>
+      <c r="P25" s="128"/>
+      <c r="Q25" s="128"/>
+      <c r="R25" s="128"/>
+      <c r="S25" s="128"/>
+      <c r="T25" s="128"/>
+      <c r="U25" s="128"/>
+      <c r="V25" s="128"/>
+      <c r="W25" s="128"/>
+      <c r="X25" s="129"/>
+      <c r="Z25" s="104"/>
+      <c r="AA25" s="105"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="5" customHeight="1" spans="2:27">
-      <c r="B26" s="75"/>
-      <c r="C26" s="76"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="80"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="80"/>
-      <c r="I26" s="80"/>
-      <c r="J26" s="80"/>
-      <c r="K26" s="80"/>
-      <c r="L26" s="80"/>
-      <c r="M26" s="80"/>
-      <c r="N26" s="80"/>
-      <c r="O26" s="80"/>
-      <c r="P26" s="80"/>
-      <c r="Q26" s="80"/>
-      <c r="R26" s="80"/>
-      <c r="S26" s="80"/>
-      <c r="T26" s="80"/>
-      <c r="U26" s="80"/>
-      <c r="V26" s="80"/>
-      <c r="W26" s="80"/>
-      <c r="X26" s="81"/>
-      <c r="Z26" s="53"/>
-      <c r="AA26" s="54"/>
+      <c r="B26" s="125"/>
+      <c r="C26" s="126"/>
+      <c r="D26" s="127"/>
+      <c r="E26" s="130"/>
+      <c r="F26" s="130"/>
+      <c r="G26" s="130"/>
+      <c r="H26" s="130"/>
+      <c r="I26" s="130"/>
+      <c r="J26" s="130"/>
+      <c r="K26" s="130"/>
+      <c r="L26" s="130"/>
+      <c r="M26" s="130"/>
+      <c r="N26" s="130"/>
+      <c r="O26" s="130"/>
+      <c r="P26" s="130"/>
+      <c r="Q26" s="130"/>
+      <c r="R26" s="130"/>
+      <c r="S26" s="130"/>
+      <c r="T26" s="130"/>
+      <c r="U26" s="130"/>
+      <c r="V26" s="130"/>
+      <c r="W26" s="130"/>
+      <c r="X26" s="131"/>
+      <c r="Z26" s="104"/>
+      <c r="AA26" s="105"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="31" customHeight="1" spans="2:27">
-      <c r="B27" s="75"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="82" t="s">
+      <c r="B27" s="125"/>
+      <c r="C27" s="126"/>
+      <c r="D27" s="127"/>
+      <c r="E27" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="F27" s="83" t="s">
+      <c r="F27" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="G27" s="84"/>
-      <c r="H27" s="85" t="s">
+      <c r="G27" s="134"/>
+      <c r="H27" s="135" t="s">
         <v>31</v>
       </c>
-      <c r="I27" s="86"/>
-      <c r="J27" s="87" t="s">
+      <c r="I27" s="136"/>
+      <c r="J27" s="137" t="s">
         <v>32</v>
       </c>
-      <c r="K27" s="88"/>
-      <c r="L27" s="88"/>
-      <c r="M27" s="88"/>
-      <c r="N27" s="88"/>
-      <c r="O27" s="88"/>
-      <c r="P27" s="88"/>
-      <c r="Q27" s="88"/>
-      <c r="R27" s="88"/>
-      <c r="S27" s="88"/>
-      <c r="T27" s="88"/>
-      <c r="U27" s="88"/>
-      <c r="V27" s="88"/>
-      <c r="W27" s="88"/>
-      <c r="X27" s="89"/>
-      <c r="Z27" s="53"/>
-      <c r="AA27" s="54"/>
+      <c r="K27" s="138"/>
+      <c r="L27" s="138"/>
+      <c r="M27" s="138"/>
+      <c r="N27" s="138"/>
+      <c r="O27" s="138"/>
+      <c r="P27" s="138"/>
+      <c r="Q27" s="138"/>
+      <c r="R27" s="138"/>
+      <c r="S27" s="138"/>
+      <c r="T27" s="138"/>
+      <c r="U27" s="138"/>
+      <c r="V27" s="138"/>
+      <c r="W27" s="138"/>
+      <c r="X27" s="139"/>
+      <c r="Z27" s="104"/>
+      <c r="AA27" s="105"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="31" customHeight="1" spans="2:27">
-      <c r="B28" s="75"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="82"/>
-      <c r="F28" s="90"/>
-      <c r="G28" s="91"/>
-      <c r="H28" s="92"/>
-      <c r="I28" s="93"/>
-      <c r="J28" s="94" t="s">
+      <c r="B28" s="125"/>
+      <c r="C28" s="126"/>
+      <c r="D28" s="127"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="140"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="142"/>
+      <c r="I28" s="143"/>
+      <c r="J28" s="144" t="s">
         <v>33</v>
       </c>
-      <c r="K28" s="95"/>
-      <c r="L28" s="95"/>
-      <c r="M28" s="95"/>
-      <c r="N28" s="95"/>
-      <c r="O28" s="95"/>
-      <c r="P28" s="95"/>
-      <c r="Q28" s="95"/>
-      <c r="R28" s="95"/>
-      <c r="S28" s="95"/>
-      <c r="T28" s="95"/>
-      <c r="U28" s="95"/>
-      <c r="V28" s="96"/>
-      <c r="W28" s="97"/>
-      <c r="X28" s="89"/>
-      <c r="Z28" s="53"/>
-      <c r="AA28" s="54"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="145"/>
+      <c r="M28" s="145"/>
+      <c r="N28" s="145"/>
+      <c r="O28" s="145"/>
+      <c r="P28" s="145"/>
+      <c r="Q28" s="145"/>
+      <c r="R28" s="145"/>
+      <c r="S28" s="145"/>
+      <c r="T28" s="145"/>
+      <c r="U28" s="145"/>
+      <c r="V28" s="146"/>
+      <c r="W28" s="147"/>
+      <c r="X28" s="139"/>
+      <c r="Z28" s="104"/>
+      <c r="AA28" s="105"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="31" customHeight="1" spans="2:27">
-      <c r="B29" s="75"/>
-      <c r="C29" s="76"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="82"/>
-      <c r="F29" s="90"/>
-      <c r="G29" s="91"/>
-      <c r="H29" s="92"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="98" t="s">
+      <c r="B29" s="125"/>
+      <c r="C29" s="126"/>
+      <c r="D29" s="127"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="142"/>
+      <c r="I29" s="143"/>
+      <c r="J29" s="148" t="s">
         <v>34</v>
       </c>
-      <c r="K29" s="99"/>
-      <c r="L29" s="99"/>
-      <c r="M29" s="99"/>
-      <c r="N29" s="100"/>
-      <c r="O29" s="100"/>
-      <c r="P29" s="100"/>
-      <c r="Q29" s="101"/>
-      <c r="R29" s="102"/>
-      <c r="S29" s="102"/>
-      <c r="T29" s="102"/>
-      <c r="U29" s="102"/>
-      <c r="V29" s="88"/>
-      <c r="W29" s="103"/>
-      <c r="X29" s="89"/>
-      <c r="Z29" s="104" t="s">
+      <c r="K29" s="149"/>
+      <c r="L29" s="149"/>
+      <c r="M29" s="149"/>
+      <c r="N29" s="150"/>
+      <c r="O29" s="150"/>
+      <c r="P29" s="150"/>
+      <c r="Q29" s="151"/>
+      <c r="R29" s="152"/>
+      <c r="S29" s="152"/>
+      <c r="T29" s="152"/>
+      <c r="U29" s="152"/>
+      <c r="V29" s="138"/>
+      <c r="W29" s="153"/>
+      <c r="X29" s="139"/>
+      <c r="Z29" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="AA29" s="105"/>
+      <c r="AA29" s="155"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="19" customHeight="1" spans="2:27">
-      <c r="B30" s="75"/>
-      <c r="C30" s="76"/>
-      <c r="D30" s="77"/>
-      <c r="E30" s="82"/>
-      <c r="F30" s="106" t="s">
+      <c r="B30" s="125"/>
+      <c r="C30" s="126"/>
+      <c r="D30" s="127"/>
+      <c r="E30" s="132"/>
+      <c r="F30" s="156" t="s">
         <v>36</v>
       </c>
-      <c r="G30" s="107"/>
-      <c r="H30" s="107"/>
-      <c r="I30" s="108"/>
-      <c r="J30" s="109" t="s">
+      <c r="G30" s="157"/>
+      <c r="H30" s="157"/>
+      <c r="I30" s="158"/>
+      <c r="J30" s="159" t="s">
         <v>37</v>
       </c>
-      <c r="K30" s="109"/>
-      <c r="L30" s="109"/>
-      <c r="M30" s="109"/>
-      <c r="N30" s="110"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="102"/>
-      <c r="Q30" s="111"/>
-      <c r="R30" s="102"/>
-      <c r="S30" s="102"/>
-      <c r="T30" s="102"/>
-      <c r="U30" s="102"/>
-      <c r="V30" s="88"/>
-      <c r="W30" s="103"/>
-      <c r="X30" s="112" t="s">
+      <c r="K30" s="159"/>
+      <c r="L30" s="159"/>
+      <c r="M30" s="159"/>
+      <c r="N30" s="160"/>
+      <c r="O30" s="152"/>
+      <c r="P30" s="152"/>
+      <c r="Q30" s="161"/>
+      <c r="R30" s="152"/>
+      <c r="S30" s="152"/>
+      <c r="T30" s="152"/>
+      <c r="U30" s="152"/>
+      <c r="V30" s="138"/>
+      <c r="W30" s="153"/>
+      <c r="X30" s="162" t="s">
         <v>38</v>
       </c>
-      <c r="Z30" s="113"/>
-      <c r="AA30" s="114"/>
+      <c r="Z30" s="163"/>
+      <c r="AA30" s="164"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="2:27">
-      <c r="B31" s="75"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="77"/>
-      <c r="E31" s="82"/>
-      <c r="F31" s="115" t="s">
+      <c r="B31" s="125"/>
+      <c r="C31" s="126"/>
+      <c r="D31" s="127"/>
+      <c r="E31" s="132"/>
+      <c r="F31" s="165" t="s">
         <v>39</v>
       </c>
-      <c r="G31" s="115"/>
-      <c r="H31" s="115"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="115" t="s">
+      <c r="G31" s="165"/>
+      <c r="H31" s="165"/>
+      <c r="I31" s="165"/>
+      <c r="J31" s="165" t="s">
         <v>40</v>
       </c>
-      <c r="K31" s="115"/>
-      <c r="L31" s="115"/>
-      <c r="M31" s="115"/>
-      <c r="N31" s="116" t="s">
+      <c r="K31" s="165"/>
+      <c r="L31" s="165"/>
+      <c r="M31" s="165"/>
+      <c r="N31" s="166" t="s">
         <v>41</v>
       </c>
-      <c r="O31" s="116"/>
-      <c r="P31" s="116"/>
-      <c r="Q31" s="116"/>
-      <c r="R31" s="116" t="s">
+      <c r="O31" s="166"/>
+      <c r="P31" s="166"/>
+      <c r="Q31" s="166"/>
+      <c r="R31" s="166" t="s">
         <v>42</v>
       </c>
-      <c r="S31" s="116"/>
-      <c r="T31" s="116"/>
-      <c r="U31" s="116"/>
-      <c r="V31" s="117" t="s">
+      <c r="S31" s="166"/>
+      <c r="T31" s="166"/>
+      <c r="U31" s="166"/>
+      <c r="V31" s="167" t="s">
         <v>43</v>
       </c>
-      <c r="W31" s="118"/>
-      <c r="X31" s="112"/>
-      <c r="Z31" s="113"/>
-      <c r="AA31" s="114"/>
+      <c r="W31" s="168"/>
+      <c r="X31" s="162"/>
+      <c r="Z31" s="163"/>
+      <c r="AA31" s="164"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="2:27">
-      <c r="B32" s="75"/>
-      <c r="C32" s="76"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="82"/>
-      <c r="F32" s="115"/>
-      <c r="G32" s="115"/>
-      <c r="H32" s="115"/>
-      <c r="I32" s="115"/>
-      <c r="J32" s="115"/>
-      <c r="K32" s="115"/>
-      <c r="L32" s="115"/>
-      <c r="M32" s="115"/>
-      <c r="N32" s="116"/>
-      <c r="O32" s="116"/>
-      <c r="P32" s="116"/>
-      <c r="Q32" s="116"/>
-      <c r="R32" s="116"/>
-      <c r="S32" s="116"/>
-      <c r="T32" s="116"/>
-      <c r="U32" s="116"/>
-      <c r="V32" s="117"/>
-      <c r="W32" s="118"/>
-      <c r="X32" s="112"/>
-      <c r="Z32" s="113"/>
-      <c r="AA32" s="114"/>
+      <c r="B32" s="125"/>
+      <c r="C32" s="126"/>
+      <c r="D32" s="127"/>
+      <c r="E32" s="132"/>
+      <c r="F32" s="165"/>
+      <c r="G32" s="165"/>
+      <c r="H32" s="165"/>
+      <c r="I32" s="165"/>
+      <c r="J32" s="165"/>
+      <c r="K32" s="165"/>
+      <c r="L32" s="165"/>
+      <c r="M32" s="165"/>
+      <c r="N32" s="166"/>
+      <c r="O32" s="166"/>
+      <c r="P32" s="166"/>
+      <c r="Q32" s="166"/>
+      <c r="R32" s="166"/>
+      <c r="S32" s="166"/>
+      <c r="T32" s="166"/>
+      <c r="U32" s="166"/>
+      <c r="V32" s="167"/>
+      <c r="W32" s="168"/>
+      <c r="X32" s="162"/>
+      <c r="Z32" s="163"/>
+      <c r="AA32" s="164"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="2:27">
-      <c r="B33" s="75"/>
-      <c r="C33" s="76"/>
-      <c r="D33" s="77"/>
-      <c r="E33" s="82"/>
-      <c r="F33" s="115"/>
-      <c r="G33" s="115"/>
-      <c r="H33" s="115"/>
-      <c r="I33" s="115"/>
-      <c r="J33" s="115"/>
-      <c r="K33" s="115"/>
-      <c r="L33" s="115"/>
-      <c r="M33" s="115"/>
-      <c r="N33" s="116"/>
-      <c r="O33" s="116"/>
-      <c r="P33" s="116"/>
-      <c r="Q33" s="116"/>
-      <c r="R33" s="116"/>
-      <c r="S33" s="116"/>
-      <c r="T33" s="116"/>
-      <c r="U33" s="116"/>
-      <c r="V33" s="117"/>
-      <c r="W33" s="118"/>
-      <c r="X33" s="112"/>
-      <c r="Z33" s="113"/>
-      <c r="AA33" s="114"/>
+      <c r="B33" s="125"/>
+      <c r="C33" s="126"/>
+      <c r="D33" s="127"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="165"/>
+      <c r="G33" s="165"/>
+      <c r="H33" s="165"/>
+      <c r="I33" s="165"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="165"/>
+      <c r="L33" s="165"/>
+      <c r="M33" s="165"/>
+      <c r="N33" s="166"/>
+      <c r="O33" s="166"/>
+      <c r="P33" s="166"/>
+      <c r="Q33" s="166"/>
+      <c r="R33" s="166"/>
+      <c r="S33" s="166"/>
+      <c r="T33" s="166"/>
+      <c r="U33" s="166"/>
+      <c r="V33" s="167"/>
+      <c r="W33" s="168"/>
+      <c r="X33" s="162"/>
+      <c r="Z33" s="163"/>
+      <c r="AA33" s="164"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="18.35" spans="2:27">
-      <c r="B34" s="75"/>
-      <c r="C34" s="119"/>
-      <c r="D34" s="120"/>
-      <c r="E34" s="82"/>
-      <c r="F34" s="121" t="s">
+      <c r="B34" s="125"/>
+      <c r="C34" s="169"/>
+      <c r="D34" s="170"/>
+      <c r="E34" s="132"/>
+      <c r="F34" s="171" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="122"/>
-      <c r="H34" s="122"/>
-      <c r="I34" s="122"/>
-      <c r="J34" s="123" t="s">
+      <c r="G34" s="172"/>
+      <c r="H34" s="172"/>
+      <c r="I34" s="172"/>
+      <c r="J34" s="173" t="s">
         <v>45</v>
       </c>
-      <c r="K34" s="123"/>
-      <c r="L34" s="176" t="s">
+      <c r="K34" s="173"/>
+      <c r="L34" s="219" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="124"/>
-      <c r="N34" s="125" t="s">
+      <c r="M34" s="174"/>
+      <c r="N34" s="175" t="s">
         <v>47</v>
       </c>
-      <c r="O34" s="125"/>
-      <c r="P34" s="177" t="s">
+      <c r="O34" s="175"/>
+      <c r="P34" s="220" t="s">
         <v>46</v>
       </c>
-      <c r="Q34" s="125"/>
-      <c r="R34" s="125" t="s">
+      <c r="Q34" s="175"/>
+      <c r="R34" s="175" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="125"/>
-      <c r="T34" s="178" t="s">
+      <c r="S34" s="175"/>
+      <c r="T34" s="221" t="s">
         <v>46</v>
       </c>
-      <c r="U34" s="126"/>
-      <c r="V34" s="127" t="s">
+      <c r="U34" s="176"/>
+      <c r="V34" s="177" t="s">
         <v>49</v>
       </c>
-      <c r="W34" s="128"/>
-      <c r="X34" s="129"/>
-      <c r="Z34" s="113"/>
-      <c r="AA34" s="114"/>
+      <c r="W34" s="178"/>
+      <c r="X34" s="179"/>
+      <c r="Z34" s="163"/>
+      <c r="AA34" s="164"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="21" customHeight="1" spans="2:27">
-      <c r="B35" s="75"/>
-      <c r="C35" s="76" t="s">
+      <c r="B35" s="125"/>
+      <c r="C35" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="130" t="s">
+      <c r="D35" s="180" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="82"/>
-      <c r="F35" s="131" t="s">
+      <c r="E35" s="132"/>
+      <c r="F35" s="181" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="132" t="s">
+      <c r="G35" s="182" t="s">
         <v>53</v>
       </c>
-      <c r="H35" s="132"/>
-      <c r="I35" s="179" t="s">
+      <c r="H35" s="182"/>
+      <c r="I35" s="222" t="s">
         <v>54</v>
       </c>
-      <c r="J35" s="133"/>
-      <c r="K35" s="132" t="s">
+      <c r="J35" s="183"/>
+      <c r="K35" s="182" t="s">
         <v>55</v>
       </c>
-      <c r="L35" s="132"/>
-      <c r="M35" s="180" t="s">
+      <c r="L35" s="182"/>
+      <c r="M35" s="223" t="s">
         <v>56</v>
       </c>
-      <c r="N35" s="134"/>
-      <c r="O35" s="132" t="s">
+      <c r="N35" s="184"/>
+      <c r="O35" s="182" t="s">
         <v>57</v>
       </c>
-      <c r="P35" s="132"/>
-      <c r="Q35" s="135" t="s">
+      <c r="P35" s="182"/>
+      <c r="Q35" s="185" t="s">
         <v>58</v>
       </c>
-      <c r="R35" s="135"/>
-      <c r="S35" s="136" t="s">
+      <c r="R35" s="185"/>
+      <c r="S35" s="186" t="s">
         <v>59</v>
       </c>
-      <c r="T35" s="136"/>
-      <c r="U35" s="179" t="s">
+      <c r="T35" s="186"/>
+      <c r="U35" s="222" t="s">
         <v>54</v>
       </c>
-      <c r="V35" s="133"/>
-      <c r="W35" s="132" t="s">
+      <c r="V35" s="183"/>
+      <c r="W35" s="182" t="s">
         <v>60</v>
       </c>
-      <c r="X35" s="137"/>
-      <c r="Z35" s="113"/>
-      <c r="AA35" s="114"/>
+      <c r="X35" s="187"/>
+      <c r="Z35" s="163"/>
+      <c r="AA35" s="164"/>
     </row>
     <row r="36" s="1" customFormat="1" spans="2:27">
-      <c r="B36" s="75"/>
-      <c r="C36" s="76"/>
-      <c r="D36" s="138"/>
-      <c r="E36" s="82"/>
-      <c r="F36" s="131"/>
-      <c r="G36" s="139" t="s">
+      <c r="B36" s="125"/>
+      <c r="C36" s="126"/>
+      <c r="D36" s="188"/>
+      <c r="E36" s="132"/>
+      <c r="F36" s="181"/>
+      <c r="G36" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="H36" s="139"/>
-      <c r="I36" s="139"/>
-      <c r="J36" s="139"/>
-      <c r="K36" s="139" t="s">
+      <c r="H36" s="189"/>
+      <c r="I36" s="189"/>
+      <c r="J36" s="189"/>
+      <c r="K36" s="189" t="s">
         <v>62</v>
       </c>
-      <c r="L36" s="139"/>
-      <c r="M36" s="139"/>
-      <c r="N36" s="139"/>
-      <c r="O36" s="139" t="s">
+      <c r="L36" s="189"/>
+      <c r="M36" s="189"/>
+      <c r="N36" s="189"/>
+      <c r="O36" s="189" t="s">
         <v>63</v>
       </c>
-      <c r="P36" s="139"/>
-      <c r="Q36" s="139"/>
-      <c r="R36" s="139"/>
-      <c r="S36" s="139" t="s">
+      <c r="P36" s="189"/>
+      <c r="Q36" s="189"/>
+      <c r="R36" s="189"/>
+      <c r="S36" s="189" t="s">
         <v>64</v>
       </c>
-      <c r="T36" s="139"/>
-      <c r="U36" s="139"/>
-      <c r="V36" s="139"/>
-      <c r="W36" s="139" t="s">
+      <c r="T36" s="189"/>
+      <c r="U36" s="189"/>
+      <c r="V36" s="189"/>
+      <c r="W36" s="189" t="s">
         <v>65</v>
       </c>
-      <c r="X36" s="140"/>
-      <c r="Z36" s="113"/>
-      <c r="AA36" s="114"/>
+      <c r="X36" s="190"/>
+      <c r="Z36" s="163"/>
+      <c r="AA36" s="164"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="2:27">
-      <c r="B37" s="75"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="138"/>
-      <c r="E37" s="82"/>
-      <c r="F37" s="131"/>
-      <c r="G37" s="139"/>
-      <c r="H37" s="139"/>
-      <c r="I37" s="139"/>
-      <c r="J37" s="139"/>
-      <c r="K37" s="139"/>
-      <c r="L37" s="139"/>
-      <c r="M37" s="139"/>
-      <c r="N37" s="139"/>
-      <c r="O37" s="139"/>
-      <c r="P37" s="139"/>
-      <c r="Q37" s="139"/>
-      <c r="R37" s="139"/>
-      <c r="S37" s="139"/>
-      <c r="T37" s="139"/>
-      <c r="U37" s="139"/>
-      <c r="V37" s="139"/>
-      <c r="W37" s="139"/>
-      <c r="X37" s="140"/>
-      <c r="Z37" s="113"/>
-      <c r="AA37" s="114"/>
+      <c r="B37" s="125"/>
+      <c r="C37" s="126"/>
+      <c r="D37" s="188"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="181"/>
+      <c r="G37" s="189"/>
+      <c r="H37" s="189"/>
+      <c r="I37" s="189"/>
+      <c r="J37" s="189"/>
+      <c r="K37" s="189"/>
+      <c r="L37" s="189"/>
+      <c r="M37" s="189"/>
+      <c r="N37" s="189"/>
+      <c r="O37" s="189"/>
+      <c r="P37" s="189"/>
+      <c r="Q37" s="189"/>
+      <c r="R37" s="189"/>
+      <c r="S37" s="189"/>
+      <c r="T37" s="189"/>
+      <c r="U37" s="189"/>
+      <c r="V37" s="189"/>
+      <c r="W37" s="189"/>
+      <c r="X37" s="190"/>
+      <c r="Z37" s="163"/>
+      <c r="AA37" s="164"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="11" customHeight="1" spans="2:27">
-      <c r="B38" s="75"/>
-      <c r="C38" s="76"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="82"/>
-      <c r="F38" s="131"/>
-      <c r="G38" s="139"/>
-      <c r="H38" s="139"/>
-      <c r="I38" s="139"/>
-      <c r="J38" s="139"/>
-      <c r="K38" s="139"/>
-      <c r="L38" s="139"/>
-      <c r="M38" s="139"/>
-      <c r="N38" s="139"/>
-      <c r="O38" s="139"/>
-      <c r="P38" s="139"/>
-      <c r="Q38" s="139"/>
-      <c r="R38" s="139"/>
-      <c r="S38" s="139"/>
-      <c r="T38" s="139"/>
-      <c r="U38" s="139"/>
-      <c r="V38" s="139"/>
-      <c r="W38" s="139"/>
-      <c r="X38" s="140"/>
-      <c r="Z38" s="113"/>
-      <c r="AA38" s="114"/>
+      <c r="B38" s="125"/>
+      <c r="C38" s="126"/>
+      <c r="D38" s="188"/>
+      <c r="E38" s="132"/>
+      <c r="F38" s="181"/>
+      <c r="G38" s="189"/>
+      <c r="H38" s="189"/>
+      <c r="I38" s="189"/>
+      <c r="J38" s="189"/>
+      <c r="K38" s="189"/>
+      <c r="L38" s="189"/>
+      <c r="M38" s="189"/>
+      <c r="N38" s="189"/>
+      <c r="O38" s="189"/>
+      <c r="P38" s="189"/>
+      <c r="Q38" s="189"/>
+      <c r="R38" s="189"/>
+      <c r="S38" s="189"/>
+      <c r="T38" s="189"/>
+      <c r="U38" s="189"/>
+      <c r="V38" s="189"/>
+      <c r="W38" s="189"/>
+      <c r="X38" s="190"/>
+      <c r="Z38" s="163"/>
+      <c r="AA38" s="164"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="18.35" spans="2:27">
-      <c r="B39" s="75"/>
-      <c r="C39" s="76"/>
-      <c r="D39" s="138"/>
-      <c r="E39" s="82"/>
-      <c r="F39" s="131"/>
-      <c r="G39" s="141" t="s">
+      <c r="B39" s="125"/>
+      <c r="C39" s="126"/>
+      <c r="D39" s="188"/>
+      <c r="E39" s="132"/>
+      <c r="F39" s="181"/>
+      <c r="G39" s="191" t="s">
         <v>66</v>
       </c>
-      <c r="H39" s="141"/>
-      <c r="I39" s="141"/>
-      <c r="J39" s="141"/>
-      <c r="K39" s="141"/>
-      <c r="L39" s="141"/>
-      <c r="M39" s="141"/>
-      <c r="N39" s="141"/>
-      <c r="O39" s="141"/>
-      <c r="P39" s="141"/>
-      <c r="Q39" s="141"/>
-      <c r="R39" s="141"/>
-      <c r="S39" s="141"/>
-      <c r="T39" s="141"/>
-      <c r="U39" s="141"/>
-      <c r="V39" s="141"/>
-      <c r="W39" s="141"/>
-      <c r="X39" s="142"/>
-      <c r="Z39" s="113"/>
-      <c r="AA39" s="114"/>
+      <c r="H39" s="191"/>
+      <c r="I39" s="191"/>
+      <c r="J39" s="191"/>
+      <c r="K39" s="191"/>
+      <c r="L39" s="191"/>
+      <c r="M39" s="191"/>
+      <c r="N39" s="191"/>
+      <c r="O39" s="191"/>
+      <c r="P39" s="191"/>
+      <c r="Q39" s="191"/>
+      <c r="R39" s="191"/>
+      <c r="S39" s="191"/>
+      <c r="T39" s="191"/>
+      <c r="U39" s="191"/>
+      <c r="V39" s="191"/>
+      <c r="W39" s="191"/>
+      <c r="X39" s="192"/>
+      <c r="Z39" s="163"/>
+      <c r="AA39" s="164"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="18.35" spans="2:27">
-      <c r="B40" s="75"/>
-      <c r="C40" s="76"/>
-      <c r="D40" s="143" t="s">
+      <c r="B40" s="125"/>
+      <c r="C40" s="126"/>
+      <c r="D40" s="193" t="s">
         <v>67</v>
       </c>
-      <c r="E40" s="143"/>
-      <c r="F40" s="143"/>
-      <c r="G40" s="143"/>
-      <c r="H40" s="143"/>
-      <c r="I40" s="143"/>
-      <c r="J40" s="143"/>
-      <c r="K40" s="143"/>
-      <c r="L40" s="143"/>
-      <c r="M40" s="143"/>
-      <c r="N40" s="143"/>
-      <c r="O40" s="143"/>
-      <c r="P40" s="143"/>
-      <c r="Q40" s="143"/>
-      <c r="R40" s="143"/>
-      <c r="S40" s="144" t="s">
+      <c r="E40" s="193"/>
+      <c r="F40" s="193"/>
+      <c r="G40" s="193"/>
+      <c r="H40" s="193"/>
+      <c r="I40" s="193"/>
+      <c r="J40" s="193"/>
+      <c r="K40" s="193"/>
+      <c r="L40" s="193"/>
+      <c r="M40" s="193"/>
+      <c r="N40" s="193"/>
+      <c r="O40" s="193"/>
+      <c r="P40" s="193"/>
+      <c r="Q40" s="193"/>
+      <c r="R40" s="193"/>
+      <c r="S40" s="194" t="s">
         <v>68</v>
       </c>
-      <c r="T40" s="145"/>
-      <c r="U40" s="145"/>
-      <c r="V40" s="145"/>
-      <c r="W40" s="145"/>
-      <c r="X40" s="146"/>
-      <c r="Z40" s="113"/>
-      <c r="AA40" s="114"/>
+      <c r="T40" s="195"/>
+      <c r="U40" s="195"/>
+      <c r="V40" s="195"/>
+      <c r="W40" s="195"/>
+      <c r="X40" s="196"/>
+      <c r="Z40" s="163"/>
+      <c r="AA40" s="164"/>
     </row>
     <row r="41" s="1" customFormat="1" spans="2:27">
-      <c r="B41" s="75"/>
-      <c r="C41" s="76"/>
-      <c r="D41" s="147" t="s">
+      <c r="B41" s="125"/>
+      <c r="C41" s="126"/>
+      <c r="D41" s="197" t="s">
         <v>69</v>
       </c>
-      <c r="E41" s="148"/>
-      <c r="F41" s="148"/>
-      <c r="G41" s="148"/>
-      <c r="H41" s="148"/>
-      <c r="I41" s="148"/>
-      <c r="J41" s="148"/>
-      <c r="K41" s="148"/>
-      <c r="L41" s="148"/>
-      <c r="M41" s="148"/>
-      <c r="N41" s="148"/>
-      <c r="O41" s="148"/>
-      <c r="P41" s="148"/>
-      <c r="Q41" s="148"/>
-      <c r="R41" s="148"/>
-      <c r="S41" s="149"/>
-      <c r="T41" s="150"/>
-      <c r="U41" s="150"/>
-      <c r="V41" s="150"/>
-      <c r="W41" s="150"/>
-      <c r="X41" s="151"/>
-      <c r="Z41" s="113"/>
-      <c r="AA41" s="114"/>
+      <c r="E41" s="198"/>
+      <c r="F41" s="198"/>
+      <c r="G41" s="198"/>
+      <c r="H41" s="198"/>
+      <c r="I41" s="198"/>
+      <c r="J41" s="198"/>
+      <c r="K41" s="198"/>
+      <c r="L41" s="198"/>
+      <c r="M41" s="198"/>
+      <c r="N41" s="198"/>
+      <c r="O41" s="198"/>
+      <c r="P41" s="198"/>
+      <c r="Q41" s="198"/>
+      <c r="R41" s="198"/>
+      <c r="S41" s="199"/>
+      <c r="T41" s="200"/>
+      <c r="U41" s="200"/>
+      <c r="V41" s="200"/>
+      <c r="W41" s="200"/>
+      <c r="X41" s="201"/>
+      <c r="Z41" s="163"/>
+      <c r="AA41" s="164"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="18" customHeight="1" spans="2:27">
-      <c r="B42" s="152" t="s">
+      <c r="B42" s="202" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="76"/>
-      <c r="D42" s="153" t="s">
+      <c r="C42" s="126"/>
+      <c r="D42" s="203" t="s">
         <v>71</v>
       </c>
-      <c r="E42" s="153"/>
-      <c r="F42" s="153"/>
-      <c r="G42" s="153"/>
-      <c r="H42" s="153"/>
-      <c r="I42" s="153"/>
-      <c r="J42" s="153"/>
-      <c r="K42" s="153"/>
-      <c r="L42" s="153"/>
-      <c r="M42" s="153"/>
-      <c r="N42" s="153"/>
-      <c r="O42" s="153"/>
-      <c r="P42" s="153"/>
-      <c r="Q42" s="153"/>
-      <c r="R42" s="153"/>
-      <c r="S42" s="154"/>
-      <c r="T42" s="155"/>
-      <c r="U42" s="155"/>
-      <c r="V42" s="155"/>
-      <c r="W42" s="155"/>
-      <c r="X42" s="156"/>
-      <c r="Z42" s="113"/>
-      <c r="AA42" s="114"/>
+      <c r="E42" s="203"/>
+      <c r="F42" s="203"/>
+      <c r="G42" s="203"/>
+      <c r="H42" s="203"/>
+      <c r="I42" s="203"/>
+      <c r="J42" s="203"/>
+      <c r="K42" s="203"/>
+      <c r="L42" s="203"/>
+      <c r="M42" s="203"/>
+      <c r="N42" s="203"/>
+      <c r="O42" s="203"/>
+      <c r="P42" s="203"/>
+      <c r="Q42" s="203"/>
+      <c r="R42" s="203"/>
+      <c r="S42" s="204"/>
+      <c r="T42" s="205"/>
+      <c r="U42" s="205"/>
+      <c r="V42" s="205"/>
+      <c r="W42" s="205"/>
+      <c r="X42" s="206"/>
+      <c r="Z42" s="163"/>
+      <c r="AA42" s="164"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="18" customHeight="1" spans="2:27">
-      <c r="B43" s="75"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="153" t="s">
+      <c r="B43" s="125"/>
+      <c r="C43" s="126"/>
+      <c r="D43" s="203" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="153"/>
-      <c r="F43" s="153"/>
-      <c r="G43" s="153"/>
-      <c r="H43" s="153"/>
-      <c r="I43" s="153"/>
-      <c r="J43" s="153"/>
-      <c r="K43" s="153"/>
-      <c r="L43" s="153"/>
-      <c r="M43" s="153"/>
-      <c r="N43" s="153"/>
-      <c r="O43" s="153"/>
-      <c r="P43" s="153"/>
-      <c r="Q43" s="153"/>
-      <c r="R43" s="153"/>
-      <c r="S43" s="154"/>
-      <c r="T43" s="155"/>
-      <c r="U43" s="155"/>
-      <c r="V43" s="155"/>
-      <c r="W43" s="155"/>
-      <c r="X43" s="156"/>
-      <c r="Z43" s="157" t="s">
+      <c r="E43" s="203"/>
+      <c r="F43" s="203"/>
+      <c r="G43" s="203"/>
+      <c r="H43" s="203"/>
+      <c r="I43" s="203"/>
+      <c r="J43" s="203"/>
+      <c r="K43" s="203"/>
+      <c r="L43" s="203"/>
+      <c r="M43" s="203"/>
+      <c r="N43" s="203"/>
+      <c r="O43" s="203"/>
+      <c r="P43" s="203"/>
+      <c r="Q43" s="203"/>
+      <c r="R43" s="203"/>
+      <c r="S43" s="204"/>
+      <c r="T43" s="205"/>
+      <c r="U43" s="205"/>
+      <c r="V43" s="205"/>
+      <c r="W43" s="205"/>
+      <c r="X43" s="206"/>
+      <c r="Z43" s="207" t="s">
         <v>73</v>
       </c>
-      <c r="AA43" s="158"/>
+      <c r="AA43" s="208"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="18" customHeight="1" spans="2:27">
-      <c r="B44" s="159"/>
-      <c r="C44" s="76"/>
-      <c r="D44" s="160" t="s">
+      <c r="B44" s="209"/>
+      <c r="C44" s="126"/>
+      <c r="D44" s="210" t="s">
         <v>74</v>
       </c>
-      <c r="E44" s="160"/>
-      <c r="F44" s="160"/>
-      <c r="G44" s="160"/>
-      <c r="H44" s="160"/>
-      <c r="I44" s="160"/>
-      <c r="J44" s="160"/>
-      <c r="K44" s="160"/>
-      <c r="L44" s="160"/>
-      <c r="M44" s="160"/>
-      <c r="N44" s="160"/>
-      <c r="O44" s="160"/>
-      <c r="P44" s="160"/>
-      <c r="Q44" s="160"/>
-      <c r="R44" s="160"/>
-      <c r="S44" s="154"/>
-      <c r="T44" s="155"/>
-      <c r="U44" s="155"/>
-      <c r="V44" s="155"/>
-      <c r="W44" s="155"/>
-      <c r="X44" s="156"/>
-      <c r="Z44" s="157"/>
-      <c r="AA44" s="158"/>
+      <c r="E44" s="210"/>
+      <c r="F44" s="210"/>
+      <c r="G44" s="210"/>
+      <c r="H44" s="210"/>
+      <c r="I44" s="210"/>
+      <c r="J44" s="210"/>
+      <c r="K44" s="210"/>
+      <c r="L44" s="210"/>
+      <c r="M44" s="210"/>
+      <c r="N44" s="210"/>
+      <c r="O44" s="210"/>
+      <c r="P44" s="210"/>
+      <c r="Q44" s="210"/>
+      <c r="R44" s="210"/>
+      <c r="S44" s="204"/>
+      <c r="T44" s="205"/>
+      <c r="U44" s="205"/>
+      <c r="V44" s="205"/>
+      <c r="W44" s="205"/>
+      <c r="X44" s="206"/>
+      <c r="Z44" s="207"/>
+      <c r="AA44" s="208"/>
     </row>
     <row r="45" s="1" customFormat="1" ht="42" customHeight="1" spans="2:27">
-      <c r="B45" s="161" t="s">
+      <c r="B45" s="211" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="162"/>
-      <c r="D45" s="163" t="s">
+      <c r="C45" s="212"/>
+      <c r="D45" s="213" t="s">
         <v>76</v>
       </c>
-      <c r="E45" s="164" t="s">
+      <c r="E45" s="214" t="s">
         <v>77</v>
       </c>
-      <c r="F45" s="164"/>
-      <c r="G45" s="164"/>
-      <c r="H45" s="164"/>
-      <c r="I45" s="164"/>
-      <c r="J45" s="164"/>
-      <c r="K45" s="164"/>
-      <c r="L45" s="164"/>
-      <c r="M45" s="164"/>
-      <c r="N45" s="164"/>
-      <c r="O45" s="164"/>
-      <c r="P45" s="164"/>
-      <c r="Q45" s="164"/>
-      <c r="R45" s="164"/>
-      <c r="S45" s="165"/>
-      <c r="T45" s="166"/>
-      <c r="U45" s="166"/>
-      <c r="V45" s="166"/>
-      <c r="W45" s="166"/>
-      <c r="X45" s="167"/>
-      <c r="Z45" s="157"/>
-      <c r="AA45" s="158"/>
+      <c r="F45" s="214"/>
+      <c r="G45" s="214"/>
+      <c r="H45" s="214"/>
+      <c r="I45" s="214"/>
+      <c r="J45" s="214"/>
+      <c r="K45" s="214"/>
+      <c r="L45" s="214"/>
+      <c r="M45" s="214"/>
+      <c r="N45" s="214"/>
+      <c r="O45" s="214"/>
+      <c r="P45" s="214"/>
+      <c r="Q45" s="214"/>
+      <c r="R45" s="214"/>
+      <c r="S45" s="215"/>
+      <c r="T45" s="216"/>
+      <c r="U45" s="216"/>
+      <c r="V45" s="216"/>
+      <c r="W45" s="216"/>
+      <c r="X45" s="217"/>
+      <c r="Z45" s="207"/>
+      <c r="AA45" s="208"/>
     </row>
     <row r="46" s="1" customFormat="1" ht="105" customHeight="1" spans="2:27">
-      <c r="B46" s="168" t="s">
+      <c r="B46" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C46" s="168"/>
-      <c r="D46" s="168"/>
-      <c r="E46" s="168"/>
-      <c r="F46" s="168"/>
-      <c r="G46" s="168"/>
-      <c r="H46" s="168"/>
-      <c r="I46" s="168"/>
-      <c r="J46" s="168"/>
-      <c r="K46" s="168"/>
-      <c r="L46" s="168"/>
-      <c r="M46" s="168"/>
-      <c r="N46" s="168"/>
-      <c r="O46" s="168"/>
-      <c r="P46" s="168"/>
-      <c r="Q46" s="168"/>
-      <c r="R46" s="168"/>
-      <c r="S46" s="168"/>
-      <c r="T46" s="168"/>
-      <c r="U46" s="168"/>
-      <c r="V46" s="168"/>
-      <c r="W46" s="168"/>
-      <c r="X46" s="168"/>
-      <c r="Z46" s="157"/>
-      <c r="AA46" s="158"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="W46" s="5"/>
+      <c r="X46" s="5"/>
+      <c r="Z46" s="207"/>
+      <c r="AA46" s="208"/>
     </row>
     <row r="47" s="1" customFormat="1" spans="2:27">
-      <c r="B47" s="168" t="s">
+      <c r="B47" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C47" s="168"/>
-      <c r="D47" s="168"/>
-      <c r="E47" s="168"/>
-      <c r="F47" s="168"/>
-      <c r="G47" s="168"/>
-      <c r="H47" s="168"/>
-      <c r="I47" s="168"/>
-      <c r="J47" s="168"/>
-      <c r="K47" s="168"/>
-      <c r="L47" s="168"/>
-      <c r="M47" s="168"/>
-      <c r="N47" s="168"/>
-      <c r="O47" s="168"/>
-      <c r="P47" s="168"/>
-      <c r="Q47" s="168"/>
-      <c r="R47" s="168"/>
-      <c r="S47" s="168"/>
-      <c r="T47" s="168"/>
-      <c r="U47" s="168"/>
-      <c r="V47" s="168"/>
-      <c r="W47" s="168"/>
-      <c r="X47" s="168"/>
-      <c r="Z47" s="157"/>
-      <c r="AA47" s="158"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+      <c r="T47" s="5"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="5"/>
+      <c r="W47" s="5"/>
+      <c r="X47" s="5"/>
+      <c r="Z47" s="207"/>
+      <c r="AA47" s="208"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="54" customHeight="1" spans="2:27">
-      <c r="B48" s="168" t="s">
+      <c r="B48" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C48" s="168"/>
-      <c r="D48" s="168"/>
-      <c r="E48" s="168"/>
-      <c r="F48" s="168"/>
-      <c r="G48" s="168"/>
-      <c r="H48" s="168"/>
-      <c r="I48" s="168"/>
-      <c r="J48" s="168"/>
-      <c r="K48" s="168"/>
-      <c r="L48" s="168"/>
-      <c r="M48" s="168"/>
-      <c r="N48" s="168"/>
-      <c r="O48" s="168"/>
-      <c r="P48" s="168"/>
-      <c r="Q48" s="168"/>
-      <c r="R48" s="168"/>
-      <c r="S48" s="168"/>
-      <c r="T48" s="168"/>
-      <c r="U48" s="168"/>
-      <c r="V48" s="168"/>
-      <c r="W48" s="168"/>
-      <c r="X48" s="168"/>
-      <c r="Z48" s="157"/>
-      <c r="AA48" s="158"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="5"/>
+      <c r="T48" s="5"/>
+      <c r="U48" s="5"/>
+      <c r="V48" s="5"/>
+      <c r="W48" s="5"/>
+      <c r="X48" s="5"/>
+      <c r="Z48" s="207"/>
+      <c r="AA48" s="208"/>
     </row>
     <row r="49" s="1" customFormat="1" ht="124" customHeight="1" spans="2:27">
-      <c r="B49" s="169" t="s">
+      <c r="B49" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="C49" s="169"/>
-      <c r="D49" s="169"/>
-      <c r="E49" s="169"/>
-      <c r="F49" s="169"/>
-      <c r="G49" s="169"/>
-      <c r="H49" s="169"/>
-      <c r="I49" s="169"/>
-      <c r="J49" s="169"/>
-      <c r="K49" s="169"/>
-      <c r="L49" s="169"/>
-      <c r="M49" s="169"/>
-      <c r="N49" s="169"/>
-      <c r="O49" s="169"/>
-      <c r="P49" s="169"/>
-      <c r="Q49" s="169"/>
-      <c r="R49" s="169"/>
-      <c r="S49" s="169"/>
-      <c r="T49" s="169"/>
-      <c r="U49" s="169"/>
-      <c r="V49" s="169"/>
-      <c r="W49" s="169"/>
-      <c r="X49" s="169"/>
-      <c r="Z49" s="157"/>
-      <c r="AA49" s="158"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
+      <c r="L49" s="42"/>
+      <c r="M49" s="42"/>
+      <c r="N49" s="42"/>
+      <c r="O49" s="42"/>
+      <c r="P49" s="42"/>
+      <c r="Q49" s="42"/>
+      <c r="R49" s="42"/>
+      <c r="S49" s="42"/>
+      <c r="T49" s="42"/>
+      <c r="U49" s="42"/>
+      <c r="V49" s="42"/>
+      <c r="W49" s="42"/>
+      <c r="X49" s="42"/>
+      <c r="Z49" s="207"/>
+      <c r="AA49" s="208"/>
     </row>
     <row r="50" s="1" customFormat="1" ht="89" customHeight="1" spans="2:27">
-      <c r="B50" s="170" t="s">
+      <c r="B50" s="218" t="s">
         <v>82</v>
       </c>
-      <c r="C50" s="170"/>
-      <c r="D50" s="170"/>
-      <c r="E50" s="170"/>
-      <c r="F50" s="170"/>
-      <c r="G50" s="170"/>
-      <c r="H50" s="170"/>
-      <c r="I50" s="170"/>
-      <c r="J50" s="170"/>
-      <c r="K50" s="170"/>
-      <c r="L50" s="170"/>
-      <c r="M50" s="170"/>
-      <c r="N50" s="170"/>
-      <c r="O50" s="170"/>
-      <c r="P50" s="170"/>
-      <c r="Q50" s="170"/>
-      <c r="R50" s="170"/>
-      <c r="S50" s="170"/>
-      <c r="T50" s="170"/>
-      <c r="U50" s="170"/>
-      <c r="V50" s="170"/>
-      <c r="W50" s="170"/>
-      <c r="X50" s="170"/>
-      <c r="Z50" s="157"/>
-      <c r="AA50" s="158"/>
-    </row>
-    <row r="51" s="2" customFormat="1" ht="3" customHeight="1" spans="2:27">
-      <c r="B51" s="171"/>
-      <c r="C51" s="171"/>
-      <c r="D51" s="171"/>
-      <c r="E51" s="171"/>
-      <c r="F51" s="171"/>
-      <c r="G51" s="171"/>
-      <c r="H51" s="171"/>
-      <c r="I51" s="171"/>
-      <c r="J51" s="171"/>
-      <c r="K51" s="171"/>
-      <c r="L51" s="171"/>
-      <c r="M51" s="171"/>
-      <c r="N51" s="171"/>
-      <c r="O51" s="171"/>
-      <c r="P51" s="171"/>
-      <c r="Q51" s="171"/>
-      <c r="R51" s="171"/>
-      <c r="S51" s="171"/>
-      <c r="T51" s="171"/>
-      <c r="U51" s="171"/>
-      <c r="V51" s="171"/>
-      <c r="W51" s="171"/>
-      <c r="X51" s="171"/>
-      <c r="Z51" s="172"/>
-      <c r="AA51" s="158"/>
+      <c r="C50" s="218"/>
+      <c r="D50" s="218"/>
+      <c r="E50" s="218"/>
+      <c r="F50" s="218"/>
+      <c r="G50" s="218"/>
+      <c r="H50" s="218"/>
+      <c r="I50" s="218"/>
+      <c r="J50" s="218"/>
+      <c r="K50" s="218"/>
+      <c r="L50" s="218"/>
+      <c r="M50" s="218"/>
+      <c r="N50" s="218"/>
+      <c r="O50" s="218"/>
+      <c r="P50" s="218"/>
+      <c r="Q50" s="218"/>
+      <c r="R50" s="218"/>
+      <c r="S50" s="218"/>
+      <c r="T50" s="218"/>
+      <c r="U50" s="218"/>
+      <c r="V50" s="218"/>
+      <c r="W50" s="218"/>
+      <c r="X50" s="218"/>
+      <c r="Z50" s="207"/>
+      <c r="AA50" s="208"/>
+    </row>
+    <row r="51" s="54" customFormat="1" ht="3" customHeight="1" spans="2:27">
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="5"/>
+      <c r="S51" s="5"/>
+      <c r="T51" s="5"/>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5"/>
+      <c r="W51" s="5"/>
+      <c r="X51" s="5"/>
+      <c r="Z51" s="208"/>
+      <c r="AA51" s="208"/>
     </row>
     <row r="52" spans="2:27">
-      <c r="B52" s="173" t="s">
+      <c r="B52" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C52" s="174"/>
-      <c r="D52" s="174"/>
-      <c r="E52" s="174"/>
-      <c r="F52" s="174"/>
-      <c r="G52" s="174"/>
-      <c r="H52" s="174"/>
-      <c r="I52" s="174"/>
-      <c r="J52" s="174"/>
-      <c r="K52" s="174"/>
-      <c r="L52" s="174"/>
-      <c r="M52" s="174"/>
-      <c r="N52" s="174"/>
-      <c r="O52" s="174"/>
-      <c r="P52" s="174"/>
-      <c r="Q52" s="174"/>
-      <c r="R52" s="174"/>
-      <c r="S52" s="174"/>
-      <c r="T52" s="174"/>
-      <c r="U52" s="174"/>
-      <c r="V52" s="174"/>
-      <c r="W52" s="174"/>
-      <c r="X52" s="174"/>
-      <c r="Y52" s="174"/>
-      <c r="Z52" s="174"/>
-      <c r="AA52" s="175"/>
-    </row>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+      <c r="O52" s="20"/>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="20"/>
+      <c r="R52" s="20"/>
+      <c r="S52" s="20"/>
+      <c r="T52" s="20"/>
+      <c r="U52" s="20"/>
+      <c r="V52" s="20"/>
+      <c r="W52" s="20"/>
+      <c r="X52" s="20"/>
+      <c r="Y52" s="20"/>
+      <c r="Z52" s="20"/>
+      <c r="AA52" s="20"/>
+    </row>
+    <row r="53" spans="2:27">
+      <c r="B53" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" ht="16.8"/>
   </sheetData>
   <mergeCells count="81">
     <mergeCell ref="Z2:AA2"/>
@@ -6700,4 +8402,1287 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A36"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="146.788461538462" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="52" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="53"/>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="53"/>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="53"/>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="53"/>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="53"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="53"/>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="53"/>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="53"/>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="53"/>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="53"/>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="53"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="53"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="53"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="53"/>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="53"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="53"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="53"/>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="53"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="53"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="53"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="53"/>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="53"/>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="53"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="53"/>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="53"/>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="53"/>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="53"/>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="53"/>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="53"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="53"/>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="53"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="53"/>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="53"/>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="53"/>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="53"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:A36"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J123"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="4.67307692307692" style="1" customWidth="1"/>
+    <col min="2" max="2" width="3.68269230769231" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5480769230769" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.73076923076923" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.2596153846154" style="2" customWidth="1"/>
+    <col min="7" max="7" width="35.7307692307692" style="2" customWidth="1"/>
+    <col min="8" max="8" width="50.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="46.5865384615385" style="1" customWidth="1"/>
+    <col min="10" max="10" width="2.83653846153846" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:10">
+      <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:10">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" customHeight="1" spans="1:10">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:10">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" customHeight="1" spans="1:10">
+      <c r="A5" s="3"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:10">
+      <c r="A6" s="3"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:10">
+      <c r="A7" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:10">
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:10">
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:10">
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:10">
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:10">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:10">
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:10">
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:10">
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" customHeight="1" spans="6:8">
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="6:8">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="6:8">
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" customHeight="1" spans="6:8">
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" customHeight="1" spans="6:8">
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" customHeight="1" spans="6:8">
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" customHeight="1" spans="6:8">
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" customHeight="1" spans="6:8">
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" customHeight="1" spans="6:8">
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" customHeight="1" spans="6:8">
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" customHeight="1" spans="6:8">
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" customHeight="1" spans="6:8">
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" customHeight="1" spans="6:8">
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" customHeight="1" spans="6:8">
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="6:8">
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" customHeight="1" spans="6:8">
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" customHeight="1" spans="6:8">
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="6:8">
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" customHeight="1" spans="6:8">
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" customHeight="1" spans="6:8">
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" customHeight="1" spans="6:8">
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" customHeight="1" spans="6:8">
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" customHeight="1" spans="6:8">
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" customHeight="1" spans="6:8">
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" customHeight="1" spans="6:8">
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" customHeight="1" spans="6:8">
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" customHeight="1" spans="6:8">
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" customHeight="1" spans="6:8">
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" customHeight="1" spans="6:8">
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" customHeight="1" spans="6:8">
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" customHeight="1" spans="6:8">
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" customHeight="1" spans="6:8">
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:8">
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:8">
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:8">
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:8">
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" customHeight="1" spans="1:8">
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:8">
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:8">
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:8">
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:8">
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" customHeight="1" spans="1:8">
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" customHeight="1" spans="1:8">
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" customHeight="1" spans="1:8">
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+    </row>
+    <row r="61" customHeight="1" spans="1:8">
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:8">
+      <c r="A63" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+    </row>
+    <row r="64" customHeight="1" spans="1:8">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+    </row>
+    <row r="65" customHeight="1" spans="1:8">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+    </row>
+    <row r="66" customHeight="1" spans="1:8">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+    </row>
+    <row r="67" customHeight="1" spans="1:8">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:8">
+      <c r="A68" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+    </row>
+    <row r="69" customHeight="1" spans="1:8">
+      <c r="A69" s="9"/>
+      <c r="B69" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10"/>
+      <c r="G69" s="10"/>
+      <c r="H69" s="10"/>
+    </row>
+    <row r="70" customHeight="1" spans="1:8">
+      <c r="A70" s="9"/>
+      <c r="B70" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D70" s="12"/>
+      <c r="E70" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+    </row>
+    <row r="71" customHeight="1" spans="1:8">
+      <c r="A71" s="9"/>
+      <c r="B71" s="14"/>
+      <c r="C71" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71" s="12"/>
+      <c r="E71" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F71" s="13"/>
+      <c r="G71" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="H71" s="15"/>
+    </row>
+    <row r="72" customHeight="1" spans="1:8">
+      <c r="A72" s="9"/>
+      <c r="B72" s="14"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="F72" s="17"/>
+      <c r="G72" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H72" s="18"/>
+    </row>
+    <row r="73" customHeight="1" spans="1:8">
+      <c r="A73" s="9"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H73" s="19"/>
+    </row>
+    <row r="74" customHeight="1" spans="1:8">
+      <c r="A74" s="9"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="H74" s="20"/>
+    </row>
+    <row r="75" customHeight="1" spans="1:8">
+      <c r="A75" s="9"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H75" s="21"/>
+    </row>
+    <row r="76" customHeight="1" spans="1:8">
+      <c r="A76" s="9"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H76" s="20"/>
+    </row>
+    <row r="77" customHeight="1" spans="1:8">
+      <c r="A77" s="9"/>
+      <c r="B77" s="14"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="H77" s="20"/>
+    </row>
+    <row r="78" customHeight="1" spans="1:8">
+      <c r="A78" s="9"/>
+      <c r="B78" s="14"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="16"/>
+      <c r="E78" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="F78" s="22"/>
+      <c r="G78" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="H78" s="23"/>
+    </row>
+    <row r="79" customHeight="1" spans="1:8">
+      <c r="A79" s="9"/>
+      <c r="B79" s="14"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F79" s="19"/>
+      <c r="G79" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H79" s="19"/>
+    </row>
+    <row r="80" customHeight="1" spans="1:8">
+      <c r="A80" s="9"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="16"/>
+      <c r="E80" s="19"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="H80" s="24"/>
+    </row>
+    <row r="81" customHeight="1" spans="1:8">
+      <c r="A81" s="9"/>
+      <c r="B81" s="14"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="16"/>
+      <c r="E81" s="19"/>
+      <c r="F81" s="19"/>
+      <c r="G81" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="H81" s="25"/>
+    </row>
+    <row r="82" customHeight="1" spans="1:8">
+      <c r="A82" s="9"/>
+      <c r="B82" s="14"/>
+      <c r="C82" s="16"/>
+      <c r="D82" s="16"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="19"/>
+      <c r="G82" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="H82" s="20"/>
+    </row>
+    <row r="83" customHeight="1" spans="1:8">
+      <c r="A83" s="9"/>
+      <c r="B83" s="14"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="H83" s="28"/>
+    </row>
+    <row r="84" customHeight="1" spans="1:8">
+      <c r="A84" s="9"/>
+      <c r="B84" s="14"/>
+      <c r="C84" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D84" s="29"/>
+      <c r="E84" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F84" s="19"/>
+      <c r="G84" s="19"/>
+      <c r="H84" s="19"/>
+    </row>
+    <row r="85" customHeight="1" spans="1:8">
+      <c r="A85" s="9"/>
+      <c r="B85" s="14"/>
+      <c r="C85" s="29"/>
+      <c r="D85" s="29"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="19"/>
+    </row>
+    <row r="86" customHeight="1" spans="1:8">
+      <c r="A86" s="30"/>
+      <c r="B86" s="31"/>
+      <c r="C86" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="D86" s="32"/>
+      <c r="E86" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+    </row>
+    <row r="87" customHeight="1" spans="1:8">
+      <c r="A87" s="30"/>
+      <c r="B87" s="31"/>
+      <c r="C87" s="33"/>
+      <c r="D87" s="33"/>
+      <c r="E87" s="34"/>
+      <c r="F87" s="34"/>
+      <c r="G87" s="34"/>
+      <c r="H87" s="34"/>
+    </row>
+    <row r="88" customHeight="1" spans="1:8">
+      <c r="A88" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B88" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C88" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D88" s="19"/>
+      <c r="E88" s="19"/>
+      <c r="F88" s="19"/>
+      <c r="G88" s="19"/>
+      <c r="H88" s="19"/>
+    </row>
+    <row r="89" customHeight="1" spans="1:8">
+      <c r="A89" s="9"/>
+      <c r="B89" s="35"/>
+      <c r="C89" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+      <c r="G89" s="36"/>
+      <c r="H89" s="36"/>
+    </row>
+    <row r="90" customHeight="1" spans="1:8">
+      <c r="A90" s="9"/>
+      <c r="B90" s="35"/>
+      <c r="C90" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="D90" s="37"/>
+      <c r="E90" s="37"/>
+      <c r="F90" s="37"/>
+      <c r="G90" s="37"/>
+      <c r="H90" s="37"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:8">
+      <c r="A91" s="9"/>
+      <c r="B91" s="35"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="37"/>
+      <c r="F91" s="37"/>
+      <c r="G91" s="37"/>
+      <c r="H91" s="37"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:8">
+      <c r="A92" s="9"/>
+      <c r="B92" s="35"/>
+      <c r="C92" s="37"/>
+      <c r="D92" s="37"/>
+      <c r="E92" s="37"/>
+      <c r="F92" s="37"/>
+      <c r="G92" s="37"/>
+      <c r="H92" s="37"/>
+    </row>
+    <row r="93" customHeight="1" spans="1:8">
+      <c r="A93" s="9"/>
+      <c r="B93" s="35"/>
+      <c r="C93" s="37"/>
+      <c r="D93" s="37"/>
+      <c r="E93" s="37"/>
+      <c r="F93" s="37"/>
+      <c r="G93" s="37"/>
+      <c r="H93" s="37"/>
+    </row>
+    <row r="94" customHeight="1" spans="1:8">
+      <c r="A94" s="9"/>
+      <c r="B94" s="35"/>
+      <c r="C94" s="37"/>
+      <c r="D94" s="37"/>
+      <c r="E94" s="37"/>
+      <c r="F94" s="37"/>
+      <c r="G94" s="37"/>
+      <c r="H94" s="37"/>
+    </row>
+    <row r="95" customHeight="1" spans="1:8">
+      <c r="A95" s="9"/>
+      <c r="B95" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="C95" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="D95" s="39"/>
+      <c r="E95" s="39"/>
+      <c r="F95" s="39"/>
+      <c r="G95" s="39"/>
+      <c r="H95" s="39"/>
+    </row>
+    <row r="96" customHeight="1" spans="1:8">
+      <c r="A96" s="9"/>
+      <c r="B96" s="35"/>
+      <c r="C96" s="29"/>
+      <c r="D96" s="29"/>
+      <c r="E96" s="29"/>
+      <c r="F96" s="29"/>
+      <c r="G96" s="29"/>
+      <c r="H96" s="29"/>
+    </row>
+    <row r="97" customHeight="1" spans="1:10">
+      <c r="A97" s="9"/>
+      <c r="B97" s="35"/>
+      <c r="C97" s="29"/>
+      <c r="D97" s="29"/>
+      <c r="E97" s="29"/>
+      <c r="F97" s="29"/>
+      <c r="G97" s="29"/>
+      <c r="H97" s="29"/>
+    </row>
+    <row r="98" customHeight="1" spans="1:10">
+      <c r="A98" s="9"/>
+      <c r="B98" s="35"/>
+      <c r="C98" s="29"/>
+      <c r="D98" s="29"/>
+      <c r="E98" s="29"/>
+      <c r="F98" s="29"/>
+      <c r="G98" s="29"/>
+      <c r="H98" s="29"/>
+    </row>
+    <row r="99" customHeight="1" spans="1:10">
+      <c r="A99" s="9"/>
+      <c r="B99" s="35"/>
+      <c r="C99" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D99" s="40"/>
+      <c r="E99" s="40"/>
+      <c r="F99" s="40"/>
+      <c r="G99" s="40"/>
+      <c r="H99" s="40"/>
+    </row>
+    <row r="100" customHeight="1" spans="1:10">
+      <c r="A100" s="9"/>
+      <c r="B100" s="35"/>
+      <c r="C100" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="D100" s="41"/>
+      <c r="E100" s="41"/>
+      <c r="F100" s="41"/>
+      <c r="G100" s="41"/>
+      <c r="H100" s="41"/>
+    </row>
+    <row r="101" customHeight="1" spans="1:10">
+      <c r="A101" s="9"/>
+      <c r="B101" s="35"/>
+      <c r="C101" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="E101" s="16"/>
+      <c r="F101" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="G101" s="42"/>
+      <c r="H101" s="42"/>
+    </row>
+    <row r="102" customHeight="1" spans="1:10">
+      <c r="A102" s="9"/>
+      <c r="B102" s="35"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="16"/>
+      <c r="F102" s="42"/>
+      <c r="G102" s="42"/>
+      <c r="H102" s="42"/>
+    </row>
+    <row r="103" customHeight="1" spans="1:10">
+      <c r="A103" s="9"/>
+      <c r="B103" s="35"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="42"/>
+      <c r="G103" s="42"/>
+      <c r="H103" s="42"/>
+    </row>
+    <row r="104" customHeight="1" spans="1:10">
+      <c r="A104" s="9"/>
+      <c r="B104" s="35"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="42"/>
+      <c r="G104" s="42"/>
+      <c r="H104" s="42"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+    </row>
+    <row r="105" customHeight="1" spans="1:10">
+      <c r="A105" s="9"/>
+      <c r="B105" s="35"/>
+      <c r="C105" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="E105" s="16"/>
+      <c r="F105" s="42"/>
+      <c r="G105" s="42"/>
+      <c r="H105" s="42"/>
+      <c r="J105" s="2"/>
+    </row>
+    <row r="106" customHeight="1" spans="1:10">
+      <c r="A106" s="9"/>
+      <c r="B106" s="35"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="42"/>
+      <c r="G106" s="42"/>
+      <c r="H106" s="42"/>
+    </row>
+    <row r="107" customHeight="1" spans="1:10">
+      <c r="A107" s="9"/>
+      <c r="B107" s="35"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="16"/>
+      <c r="E107" s="16"/>
+      <c r="F107" s="42"/>
+      <c r="G107" s="42"/>
+      <c r="H107" s="42"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:10">
+      <c r="A108" s="9"/>
+      <c r="B108" s="35"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="16"/>
+      <c r="E108" s="16"/>
+      <c r="F108" s="42"/>
+      <c r="G108" s="42"/>
+      <c r="H108" s="42"/>
+    </row>
+    <row r="109" customHeight="1" spans="1:10">
+      <c r="A109" s="9"/>
+      <c r="B109" s="35"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="16"/>
+      <c r="F109" s="42"/>
+      <c r="G109" s="42"/>
+      <c r="H109" s="42"/>
+    </row>
+    <row r="110" customHeight="1" spans="1:10">
+      <c r="A110" s="9"/>
+      <c r="B110" s="35"/>
+      <c r="C110" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D110" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="E110" s="16"/>
+      <c r="F110" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="G110" s="42"/>
+      <c r="H110" s="42"/>
+    </row>
+    <row r="111" customHeight="1" spans="1:10">
+      <c r="A111" s="9"/>
+      <c r="B111" s="35"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="16"/>
+      <c r="E111" s="16"/>
+      <c r="F111" s="42"/>
+      <c r="G111" s="42"/>
+      <c r="H111" s="42"/>
+    </row>
+    <row r="112" customHeight="1" spans="1:10">
+      <c r="A112" s="9"/>
+      <c r="B112" s="35"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="16"/>
+      <c r="E112" s="16"/>
+      <c r="F112" s="42"/>
+      <c r="G112" s="42"/>
+      <c r="H112" s="42"/>
+    </row>
+    <row r="113" customHeight="1" spans="1:8">
+      <c r="A113" s="9"/>
+      <c r="B113" s="35"/>
+      <c r="C113" s="5"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="42"/>
+      <c r="G113" s="42"/>
+      <c r="H113" s="42"/>
+    </row>
+    <row r="114" customHeight="1" spans="1:8">
+      <c r="A114" s="9"/>
+      <c r="B114" s="35"/>
+      <c r="C114" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D114" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="E114" s="29"/>
+      <c r="F114" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G114" s="5"/>
+      <c r="H114" s="5"/>
+    </row>
+    <row r="115" customHeight="1" spans="1:8">
+      <c r="A115" s="9"/>
+      <c r="B115" s="35"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="29"/>
+      <c r="E115" s="29"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="5"/>
+    </row>
+    <row r="116" customHeight="1" spans="1:8">
+      <c r="A116" s="9"/>
+      <c r="B116" s="35"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="29"/>
+      <c r="E116" s="29"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="5"/>
+    </row>
+    <row r="117" customHeight="1" spans="1:8">
+      <c r="A117" s="9"/>
+      <c r="B117" s="35"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="29"/>
+      <c r="E117" s="29"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+    </row>
+    <row r="118" customHeight="1" spans="1:8">
+      <c r="A118" s="9"/>
+      <c r="B118" s="35"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="29"/>
+      <c r="E118" s="29"/>
+      <c r="F118" s="5"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5"/>
+    </row>
+    <row r="119" customHeight="1" spans="1:8">
+      <c r="A119" s="43"/>
+      <c r="B119" s="44"/>
+      <c r="C119" s="45"/>
+      <c r="D119" s="46"/>
+      <c r="E119" s="46"/>
+      <c r="F119" s="45"/>
+      <c r="G119" s="45"/>
+      <c r="H119" s="45"/>
+    </row>
+    <row r="120" customHeight="1" spans="1:8">
+      <c r="A120" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="B120" s="47"/>
+      <c r="C120" s="47"/>
+      <c r="D120" s="47"/>
+      <c r="E120" s="47"/>
+      <c r="F120" s="47"/>
+      <c r="G120" s="47"/>
+      <c r="H120" s="47"/>
+    </row>
+    <row r="121" customHeight="1" spans="1:8">
+      <c r="A121" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="B121" s="49"/>
+      <c r="C121" s="49"/>
+      <c r="D121" s="49"/>
+      <c r="E121" s="49"/>
+      <c r="F121" s="49"/>
+      <c r="G121" s="49"/>
+      <c r="H121" s="49"/>
+    </row>
+    <row r="122" customHeight="1" spans="1:8">
+      <c r="A122" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122" s="50"/>
+      <c r="C122" s="50"/>
+      <c r="D122" s="50"/>
+      <c r="E122" s="50"/>
+      <c r="F122" s="50"/>
+      <c r="G122" s="50"/>
+      <c r="H122" s="50"/>
+    </row>
+    <row r="123" customHeight="1" spans="1:8">
+      <c r="A123" s="51"/>
+      <c r="B123" s="51"/>
+      <c r="C123" s="51"/>
+      <c r="D123" s="51"/>
+      <c r="E123" s="51"/>
+      <c r="F123" s="51"/>
+      <c r="G123" s="51"/>
+      <c r="H123" s="51"/>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="B68:H68"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="G83:H83"/>
+    <mergeCell ref="C88:H88"/>
+    <mergeCell ref="C89:H89"/>
+    <mergeCell ref="C99:H99"/>
+    <mergeCell ref="C100:H100"/>
+    <mergeCell ref="A120:H120"/>
+    <mergeCell ref="A121:H121"/>
+    <mergeCell ref="A68:A87"/>
+    <mergeCell ref="A88:A119"/>
+    <mergeCell ref="B70:B87"/>
+    <mergeCell ref="B88:B94"/>
+    <mergeCell ref="B95:B119"/>
+    <mergeCell ref="C101:C104"/>
+    <mergeCell ref="C105:C109"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="C114:C119"/>
+    <mergeCell ref="C86:D87"/>
+    <mergeCell ref="E86:H87"/>
+    <mergeCell ref="A1:G6"/>
+    <mergeCell ref="H1:I6"/>
+    <mergeCell ref="A7:G61"/>
+    <mergeCell ref="H7:I61"/>
+    <mergeCell ref="A63:H67"/>
+    <mergeCell ref="C71:D83"/>
+    <mergeCell ref="E72:F77"/>
+    <mergeCell ref="E79:F83"/>
+    <mergeCell ref="C84:D85"/>
+    <mergeCell ref="E84:H85"/>
+    <mergeCell ref="C90:H94"/>
+    <mergeCell ref="C95:H98"/>
+    <mergeCell ref="D101:E104"/>
+    <mergeCell ref="F101:H109"/>
+    <mergeCell ref="D105:E109"/>
+    <mergeCell ref="D110:E113"/>
+    <mergeCell ref="F110:H113"/>
+    <mergeCell ref="D114:E119"/>
+    <mergeCell ref="F114:H119"/>
+    <mergeCell ref="A122:H123"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>